--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -727,6 +727,9 @@
       <c r="P8">
         <v>4</v>
       </c>
+      <c r="Q8" s="1">
+        <v>46063</v>
+      </c>
     </row>
     <row r="9" spans="1:17">
       <c r="A9" s="1">
@@ -759,6 +762,9 @@
       <c r="P9">
         <v>26</v>
       </c>
+      <c r="Q9" s="1">
+        <v>46063</v>
+      </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1">
@@ -1679,6 +1685,9 @@
       </c>
       <c r="F37" t="s">
         <v>22</v>
+      </c>
+      <c r="O37" s="1">
+        <v>46064</v>
       </c>
     </row>
     <row r="38" spans="1:16">

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -84,7 +84,7 @@
     <t>Machine Number</t>
   </si>
   <si>
-    <t>KASAB FLUTE</t>
+    <t>SUNSHINE</t>
   </si>
 </sst>
 </file>
@@ -1689,6 +1689,9 @@
       <c r="O37" s="1">
         <v>46064</v>
       </c>
+      <c r="P37">
+        <v>26</v>
+      </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" s="1">

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="23">
   <si>
     <t>ENDS</t>
   </si>
@@ -420,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q39"/>
+  <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1660,6 +1660,24 @@
       <c r="F36" t="s">
         <v>4</v>
       </c>
+      <c r="G36">
+        <v>56</v>
+      </c>
+      <c r="H36">
+        <v>4</v>
+      </c>
+      <c r="I36">
+        <v>1050</v>
+      </c>
+      <c r="K36">
+        <v>9</v>
+      </c>
+      <c r="L36">
+        <v>662</v>
+      </c>
+      <c r="M36" t="s">
+        <v>11</v>
+      </c>
       <c r="O36" s="1">
         <v>46062</v>
       </c>
@@ -1686,6 +1704,24 @@
       <c r="F37" t="s">
         <v>22</v>
       </c>
+      <c r="G37">
+        <v>6</v>
+      </c>
+      <c r="H37">
+        <v>19</v>
+      </c>
+      <c r="I37">
+        <v>1030</v>
+      </c>
+      <c r="K37">
+        <v>9</v>
+      </c>
+      <c r="L37">
+        <v>630</v>
+      </c>
+      <c r="M37" t="s">
+        <v>11</v>
+      </c>
       <c r="O37" s="1">
         <v>46064</v>
       </c>
@@ -1712,10 +1748,28 @@
       <c r="F38" t="s">
         <v>4</v>
       </c>
+      <c r="G38">
+        <v>47</v>
+      </c>
+      <c r="H38">
+        <v>10</v>
+      </c>
+      <c r="I38">
+        <v>1050</v>
+      </c>
+      <c r="K38">
+        <v>9</v>
+      </c>
+      <c r="L38">
+        <v>662</v>
+      </c>
+      <c r="M38" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" s="1">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B39">
         <v>152</v>
@@ -1731,6 +1785,106 @@
       </c>
       <c r="F39" t="s">
         <v>4</v>
+      </c>
+      <c r="G39">
+        <v>18</v>
+      </c>
+      <c r="H39">
+        <v>10</v>
+      </c>
+      <c r="I39">
+        <v>1050</v>
+      </c>
+      <c r="K39">
+        <v>9</v>
+      </c>
+      <c r="L39">
+        <v>662</v>
+      </c>
+      <c r="M39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B40">
+        <v>153</v>
+      </c>
+      <c r="C40">
+        <v>6800</v>
+      </c>
+      <c r="D40">
+        <v>6720</v>
+      </c>
+      <c r="E40">
+        <v>56</v>
+      </c>
+      <c r="F40" t="s">
+        <v>19</v>
+      </c>
+      <c r="G40">
+        <v>20</v>
+      </c>
+      <c r="H40">
+        <v>12</v>
+      </c>
+      <c r="I40">
+        <v>915</v>
+      </c>
+      <c r="K40">
+        <v>10</v>
+      </c>
+      <c r="L40">
+        <v>672</v>
+      </c>
+      <c r="M40" t="s">
+        <v>12</v>
+      </c>
+      <c r="O40" s="1">
+        <v>46064</v>
+      </c>
+      <c r="P40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B41">
+        <v>154</v>
+      </c>
+      <c r="C41">
+        <v>6750</v>
+      </c>
+      <c r="D41">
+        <v>6720</v>
+      </c>
+      <c r="E41">
+        <v>56</v>
+      </c>
+      <c r="F41" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41">
+        <v>9</v>
+      </c>
+      <c r="H41">
+        <v>8</v>
+      </c>
+      <c r="I41">
+        <v>915</v>
+      </c>
+      <c r="K41">
+        <v>10</v>
+      </c>
+      <c r="L41">
+        <v>672</v>
+      </c>
+      <c r="M41" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -558,6 +558,9 @@
       <c r="P3">
         <v>22</v>
       </c>
+      <c r="Q3" s="1">
+        <v>46064</v>
+      </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="1">
@@ -1885,6 +1888,12 @@
       </c>
       <c r="M41" t="s">
         <v>12</v>
+      </c>
+      <c r="O41" s="1">
+        <v>46065</v>
+      </c>
+      <c r="P41">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="26">
   <si>
     <t>ENDS</t>
   </si>
@@ -85,16 +85,32 @@
   </si>
   <si>
     <t>SUNSHINE</t>
+  </si>
+  <si>
+    <t>Re-Loading Date</t>
+  </si>
+  <si>
+    <t>Re-Machine Number</t>
+  </si>
+  <si>
+    <t>Re-Bhidan Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -120,12 +136,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -420,17 +442,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="29.25" customHeight="1">
+    <row r="1" spans="1:20" s="2" customFormat="1" ht="29.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -479,8 +502,17 @@
       <c r="Q1" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="1">
         <v>46022</v>
       </c>
@@ -527,7 +559,7 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:20">
       <c r="A3" s="1">
         <v>46027</v>
       </c>
@@ -562,7 +594,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:20">
       <c r="A4" s="1">
         <v>46028</v>
       </c>
@@ -597,7 +629,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:20">
       <c r="A5" s="1">
         <v>46031</v>
       </c>
@@ -632,7 +664,7 @@
         <v>46061</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:20">
       <c r="A6" s="1">
         <v>46031</v>
       </c>
@@ -667,7 +699,7 @@
         <v>46062</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:20">
       <c r="A7" s="1">
         <v>46032</v>
       </c>
@@ -699,7 +731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:20">
       <c r="A8" s="1">
         <v>46033</v>
       </c>
@@ -734,7 +766,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:20">
       <c r="A9" s="1">
         <v>46034</v>
       </c>
@@ -769,7 +801,7 @@
         <v>46063</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:20">
       <c r="A10" s="1">
         <v>46035</v>
       </c>
@@ -801,7 +833,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:20">
       <c r="A11" s="1">
         <v>46035</v>
       </c>
@@ -832,8 +864,11 @@
       <c r="P11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="Q11" s="5">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="A12" s="1">
         <v>46036</v>
       </c>
@@ -865,7 +900,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:20">
       <c r="A13" s="1">
         <v>46040</v>
       </c>
@@ -894,7 +929,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:20">
       <c r="A14" s="1">
         <v>46041</v>
       </c>
@@ -923,7 +958,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:20">
       <c r="A15" s="1">
         <v>46042</v>
       </c>
@@ -952,7 +987,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:20">
       <c r="A16" s="1">
         <v>46044</v>
       </c>
@@ -979,6 +1014,15 @@
       </c>
       <c r="P16">
         <v>1</v>
+      </c>
+      <c r="Q16" s="5">
+        <v>46063</v>
+      </c>
+      <c r="R16" s="5">
+        <v>46064</v>
+      </c>
+      <c r="S16" s="6">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1898,6 +1942,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -100,17 +100,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -136,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -146,8 +139,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,7 +447,7 @@
     <col min="19" max="19" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="2" customFormat="1" ht="29.25" customHeight="1">
+    <row r="1" spans="1:20" s="2" customFormat="1" ht="42.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -864,9 +858,9 @@
       <c r="P11">
         <v>10</v>
       </c>
-      <c r="Q11" s="5">
-        <v>46063</v>
-      </c>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="7"/>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1">
@@ -899,6 +893,9 @@
       <c r="P12">
         <v>8</v>
       </c>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="7"/>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1">
@@ -928,6 +925,9 @@
       <c r="P13">
         <v>24</v>
       </c>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="7"/>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1">
@@ -957,6 +957,9 @@
       <c r="P14">
         <v>28</v>
       </c>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="7"/>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1">
@@ -986,6 +989,9 @@
       <c r="P15">
         <v>25</v>
       </c>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="7"/>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1">
@@ -1015,15 +1021,9 @@
       <c r="P16">
         <v>1</v>
       </c>
-      <c r="Q16" s="5">
-        <v>46063</v>
-      </c>
-      <c r="R16" s="5">
-        <v>46064</v>
-      </c>
-      <c r="S16" s="6">
-        <v>10</v>
-      </c>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="7"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1">

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="26">
   <si>
     <t>ENDS</t>
   </si>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -826,6 +826,9 @@
       <c r="P10">
         <v>6</v>
       </c>
+      <c r="Q10" s="1">
+        <v>46066</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1">
@@ -925,7 +928,9 @@
       <c r="P13">
         <v>24</v>
       </c>
-      <c r="Q13" s="6"/>
+      <c r="Q13" s="5">
+        <v>46065</v>
+      </c>
       <c r="R13" s="6"/>
       <c r="S13" s="7"/>
     </row>
@@ -1938,6 +1943,208 @@
       </c>
       <c r="P41">
         <v>22</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B42">
+        <v>155</v>
+      </c>
+      <c r="C42">
+        <v>6800</v>
+      </c>
+      <c r="D42">
+        <v>6720</v>
+      </c>
+      <c r="E42">
+        <v>56</v>
+      </c>
+      <c r="F42" t="s">
+        <v>19</v>
+      </c>
+      <c r="G42">
+        <v>23</v>
+      </c>
+      <c r="H42">
+        <v>6</v>
+      </c>
+      <c r="I42">
+        <v>915</v>
+      </c>
+      <c r="K42">
+        <v>10</v>
+      </c>
+      <c r="L42">
+        <v>672</v>
+      </c>
+      <c r="M42" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B43">
+        <v>156</v>
+      </c>
+      <c r="C43">
+        <v>6750</v>
+      </c>
+      <c r="D43">
+        <v>6720</v>
+      </c>
+      <c r="E43">
+        <v>56</v>
+      </c>
+      <c r="F43" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43">
+        <v>43</v>
+      </c>
+      <c r="H43">
+        <v>10</v>
+      </c>
+      <c r="I43">
+        <v>915</v>
+      </c>
+      <c r="K43">
+        <v>10</v>
+      </c>
+      <c r="L43">
+        <v>672</v>
+      </c>
+      <c r="M43" t="s">
+        <v>12</v>
+      </c>
+      <c r="O43" s="1">
+        <v>46067</v>
+      </c>
+      <c r="P43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B44">
+        <v>157</v>
+      </c>
+      <c r="C44">
+        <v>8000</v>
+      </c>
+      <c r="D44">
+        <v>5670</v>
+      </c>
+      <c r="E44">
+        <v>54</v>
+      </c>
+      <c r="F44" t="s">
+        <v>22</v>
+      </c>
+      <c r="G44">
+        <v>35</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>1030</v>
+      </c>
+      <c r="K44">
+        <v>9</v>
+      </c>
+      <c r="L44">
+        <v>630</v>
+      </c>
+      <c r="M44" t="s">
+        <v>12</v>
+      </c>
+      <c r="O44" s="1">
+        <v>46066</v>
+      </c>
+      <c r="P44">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B45">
+        <v>158</v>
+      </c>
+      <c r="C45">
+        <v>4000</v>
+      </c>
+      <c r="D45">
+        <v>5670</v>
+      </c>
+      <c r="E45">
+        <v>54</v>
+      </c>
+      <c r="F45" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45">
+        <v>38</v>
+      </c>
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>1030</v>
+      </c>
+      <c r="K45">
+        <v>9</v>
+      </c>
+      <c r="L45">
+        <v>630</v>
+      </c>
+      <c r="M45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="1">
+        <v>46067</v>
+      </c>
+      <c r="B46">
+        <v>159</v>
+      </c>
+      <c r="C46">
+        <v>3800</v>
+      </c>
+      <c r="D46">
+        <v>5670</v>
+      </c>
+      <c r="E46">
+        <v>54</v>
+      </c>
+      <c r="F46" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46">
+        <v>33</v>
+      </c>
+      <c r="H46">
+        <v>11</v>
+      </c>
+      <c r="I46">
+        <v>1030</v>
+      </c>
+      <c r="K46">
+        <v>9</v>
+      </c>
+      <c r="L46">
+        <v>630</v>
+      </c>
+      <c r="M46" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -962,7 +962,9 @@
       <c r="P14">
         <v>28</v>
       </c>
-      <c r="Q14" s="6"/>
+      <c r="Q14" s="5">
+        <v>46067</v>
+      </c>
       <c r="R14" s="6"/>
       <c r="S14" s="7"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -962,9 +962,7 @@
       <c r="P14">
         <v>28</v>
       </c>
-      <c r="Q14" s="5">
-        <v>46067</v>
-      </c>
+      <c r="Q14" s="5"/>
       <c r="R14" s="6"/>
       <c r="S14" s="7"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -724,6 +724,9 @@
       <c r="P7">
         <v>5</v>
       </c>
+      <c r="Q7" s="1">
+        <v>46067</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1">
@@ -962,7 +965,9 @@
       <c r="P14">
         <v>28</v>
       </c>
-      <c r="Q14" s="5"/>
+      <c r="Q14" s="5">
+        <v>46067</v>
+      </c>
       <c r="R14" s="6"/>
       <c r="S14" s="7"/>
     </row>
@@ -1561,7 +1566,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:17">
       <c r="A33" s="1">
         <v>46058</v>
       </c>
@@ -1605,7 +1610,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:17">
       <c r="A34" s="1">
         <v>46059</v>
       </c>
@@ -1649,7 +1654,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:17">
       <c r="A35" s="1">
         <v>46059</v>
       </c>
@@ -1693,7 +1698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:16">
+    <row r="36" spans="1:17">
       <c r="A36" s="1">
         <v>46060</v>
       </c>
@@ -1737,7 +1742,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:16">
+    <row r="37" spans="1:17">
       <c r="A37" s="1">
         <v>46061</v>
       </c>
@@ -1781,7 +1786,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:16">
+    <row r="38" spans="1:17">
       <c r="A38" s="1">
         <v>46062</v>
       </c>
@@ -1819,7 +1824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:17">
       <c r="A39" s="1">
         <v>46063</v>
       </c>
@@ -1857,7 +1862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:16">
+    <row r="40" spans="1:17">
       <c r="A40" s="1">
         <v>46063</v>
       </c>
@@ -1901,7 +1906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:17">
       <c r="A41" s="1">
         <v>46064</v>
       </c>
@@ -1945,7 +1950,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:17">
       <c r="A42" s="1">
         <v>46065</v>
       </c>
@@ -1983,7 +1988,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:16">
+    <row r="43" spans="1:17">
       <c r="A43" s="1">
         <v>46065</v>
       </c>
@@ -2027,7 +2032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:16">
+    <row r="44" spans="1:17">
       <c r="A44" s="1">
         <v>46066</v>
       </c>
@@ -2070,8 +2075,9 @@
       <c r="P44">
         <v>24</v>
       </c>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="Q44" s="1"/>
+    </row>
+    <row r="45" spans="1:17">
       <c r="A45" s="1">
         <v>46066</v>
       </c>
@@ -2108,8 +2114,14 @@
       <c r="M45" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="O45" s="1">
+        <v>46068</v>
+      </c>
+      <c r="P45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
       <c r="A46" s="1">
         <v>46067</v>
       </c>
@@ -2145,6 +2157,12 @@
       </c>
       <c r="M46" t="s">
         <v>12</v>
+      </c>
+      <c r="O46" s="1">
+        <v>46068</v>
+      </c>
+      <c r="P46">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -596,7 +596,7 @@
         <v>115</v>
       </c>
       <c r="C4">
-        <v>3700</v>
+        <v>3300</v>
       </c>
       <c r="D4">
         <v>5958</v>
@@ -736,7 +736,7 @@
         <v>121</v>
       </c>
       <c r="C8">
-        <v>3600</v>
+        <v>3300</v>
       </c>
       <c r="D8">
         <v>5624</v>
@@ -771,7 +771,7 @@
         <v>122</v>
       </c>
       <c r="C9">
-        <v>4300</v>
+        <v>4000</v>
       </c>
       <c r="D9">
         <v>5624</v>
@@ -911,7 +911,7 @@
         <v>126</v>
       </c>
       <c r="C13">
-        <v>6700</v>
+        <v>5100</v>
       </c>
       <c r="D13">
         <v>5624</v>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -6712,7 +6712,12 @@
       <c r="Q135">
         <v>22</v>
       </c>
-      <c r="R135" s="1"/>
+      <c r="R135" s="1">
+        <v>46189</v>
+      </c>
+      <c r="S135" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="136" spans="1:24">
       <c r="A136" s="1">
@@ -7052,7 +7057,12 @@
       <c r="Q142">
         <v>5</v>
       </c>
-      <c r="R142" s="1"/>
+      <c r="R142" s="1">
+        <v>46189</v>
+      </c>
+      <c r="S142" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="143" spans="1:24">
       <c r="A143" s="1">
@@ -8141,6 +8151,15 @@
       <c r="M166" t="s">
         <v>45</v>
       </c>
+      <c r="O166" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P166" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q166">
+        <v>22</v>
+      </c>
       <c r="R166" s="1"/>
     </row>
     <row r="167" spans="1:18">
@@ -8321,6 +8340,15 @@
       <c r="M170" t="s">
         <v>55</v>
       </c>
+      <c r="O170" s="1">
+        <v>46189</v>
+      </c>
+      <c r="P170" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q170">
+        <v>5</v>
+      </c>
       <c r="R170" s="1"/>
     </row>
     <row r="171" spans="1:18">
@@ -8599,6 +8627,15 @@
       </c>
       <c r="M177" t="s">
         <v>55</v>
+      </c>
+      <c r="O177" s="1">
+        <v>46188</v>
+      </c>
+      <c r="P177" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q177">
+        <v>27</v>
       </c>
       <c r="R177" s="1"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -6664,7 +6664,12 @@
       <c r="Q134">
         <v>1</v>
       </c>
-      <c r="R134" s="1"/>
+      <c r="R134" s="1">
+        <v>46191</v>
+      </c>
+      <c r="S134" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="135" spans="1:24">
       <c r="A135" s="1">
@@ -6765,7 +6770,12 @@
       <c r="Q136">
         <v>18</v>
       </c>
-      <c r="R136" s="1"/>
+      <c r="R136" s="1">
+        <v>46191</v>
+      </c>
+      <c r="S136" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="137" spans="1:24">
       <c r="A137" s="1">
@@ -6863,7 +6873,12 @@
       <c r="Q138">
         <v>6</v>
       </c>
-      <c r="R138" s="1"/>
+      <c r="R138" s="1">
+        <v>46191</v>
+      </c>
+      <c r="S138" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="139" spans="1:24">
       <c r="A139" s="1">
@@ -6961,7 +6976,12 @@
       <c r="Q140">
         <v>12</v>
       </c>
-      <c r="R140" s="1"/>
+      <c r="R140" s="1">
+        <v>46192</v>
+      </c>
+      <c r="S140" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="141" spans="1:24">
       <c r="A141" s="1">
@@ -8702,6 +8722,15 @@
       </c>
       <c r="M179" t="s">
         <v>45</v>
+      </c>
+      <c r="O179" s="1">
+        <v>46192</v>
+      </c>
+      <c r="P179" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q179">
+        <v>1</v>
       </c>
       <c r="R179" s="1"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$180</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -8576,6 +8576,15 @@
       <c r="M175" t="s">
         <v>45</v>
       </c>
+      <c r="O175" s="1">
+        <v>46194</v>
+      </c>
+      <c r="P175" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q175">
+        <v>12</v>
+      </c>
       <c r="R175" s="1"/>
     </row>
     <row r="176" spans="1:18">
@@ -8980,7 +8989,7 @@
       <c r="A235" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X175">
+  <autoFilter ref="A1:X180">
     <filterColumn colId="5"/>
     <filterColumn colId="13"/>
   </autoFilter>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$187</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -542,6 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -636,7 +637,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
+    <row r="2" spans="1:24" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
       <c r="A2" s="6">
         <v>45976</v>
       </c>
@@ -674,7 +675,7 @@
       <c r="V2" s="7"/>
       <c r="X2" s="5"/>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" hidden="1">
       <c r="A3" s="1">
         <v>46022</v>
       </c>
@@ -723,7 +724,7 @@
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" hidden="1">
       <c r="A4" s="1">
         <v>46027</v>
       </c>
@@ -760,7 +761,7 @@
       </c>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" hidden="1">
       <c r="A5" s="1">
         <v>46028</v>
       </c>
@@ -797,7 +798,7 @@
       </c>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:24" hidden="1">
       <c r="A6" s="1">
         <v>46031</v>
       </c>
@@ -834,7 +835,7 @@
       </c>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" hidden="1">
       <c r="A7" s="1">
         <v>46031</v>
       </c>
@@ -871,7 +872,7 @@
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:24" hidden="1">
       <c r="A8" s="1">
         <v>46032</v>
       </c>
@@ -910,7 +911,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:24" hidden="1">
       <c r="A9" s="1">
         <v>46033</v>
       </c>
@@ -947,7 +948,7 @@
       </c>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" hidden="1">
       <c r="A10" s="1">
         <v>46034</v>
       </c>
@@ -984,7 +985,7 @@
       </c>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:24" hidden="1">
       <c r="A11" s="1">
         <v>46035</v>
       </c>
@@ -1021,7 +1022,7 @@
       </c>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:24" hidden="1">
       <c r="A12" s="1">
         <v>46035</v>
       </c>
@@ -1063,7 +1064,7 @@
       <c r="U12" s="4"/>
       <c r="V12" s="9"/>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:24" hidden="1">
       <c r="A13" s="1">
         <v>46036</v>
       </c>
@@ -1105,7 +1106,7 @@
       <c r="U13" s="4"/>
       <c r="V13" s="9"/>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" hidden="1">
       <c r="A14" s="1">
         <v>46040</v>
       </c>
@@ -1142,7 +1143,7 @@
       <c r="U14" s="4"/>
       <c r="V14" s="9"/>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" hidden="1">
       <c r="A15" s="1">
         <v>46041</v>
       </c>
@@ -1181,7 +1182,7 @@
       <c r="U15" s="4"/>
       <c r="V15" s="9"/>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:24" hidden="1">
       <c r="A16" s="1">
         <v>46042</v>
       </c>
@@ -1220,7 +1221,7 @@
       <c r="U16" s="4"/>
       <c r="V16" s="9"/>
     </row>
-    <row r="17" spans="1:24">
+    <row r="17" spans="1:24" hidden="1">
       <c r="A17" s="1">
         <v>46044</v>
       </c>
@@ -1271,7 +1272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:24">
+    <row r="18" spans="1:24" hidden="1">
       <c r="A18" s="1">
         <v>46044</v>
       </c>
@@ -1307,7 +1308,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24">
+    <row r="19" spans="1:24" hidden="1">
       <c r="A19" s="1">
         <v>46046</v>
       </c>
@@ -1343,7 +1344,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:24">
+    <row r="20" spans="1:24" hidden="1">
       <c r="A20" s="1">
         <v>46047</v>
       </c>
@@ -1379,7 +1380,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:24">
+    <row r="21" spans="1:24" hidden="1">
       <c r="A21" s="1">
         <v>46047</v>
       </c>
@@ -1415,7 +1416,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:24">
+    <row r="22" spans="1:24" hidden="1">
       <c r="A22" s="1">
         <v>46050</v>
       </c>
@@ -1468,7 +1469,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:24">
+    <row r="23" spans="1:24" hidden="1">
       <c r="A23" s="1">
         <v>46050</v>
       </c>
@@ -1504,7 +1505,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:24">
+    <row r="24" spans="1:24" hidden="1">
       <c r="A24" s="1">
         <v>46051</v>
       </c>
@@ -1545,7 +1546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
+    <row r="25" spans="1:24" hidden="1">
       <c r="A25" s="1">
         <v>46051</v>
       </c>
@@ -1581,7 +1582,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
+    <row r="26" spans="1:24" hidden="1">
       <c r="A26" s="1">
         <v>46052</v>
       </c>
@@ -1617,7 +1618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:24" hidden="1">
       <c r="A27" s="1">
         <v>46052</v>
       </c>
@@ -1653,7 +1654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
+    <row r="28" spans="1:24" hidden="1">
       <c r="A28" s="1">
         <v>46053</v>
       </c>
@@ -1689,7 +1690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
+    <row r="29" spans="1:24" hidden="1">
       <c r="A29" s="1">
         <v>46053</v>
       </c>
@@ -1740,7 +1741,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:24">
+    <row r="30" spans="1:24" hidden="1">
       <c r="A30" s="1">
         <v>46053</v>
       </c>
@@ -1855,7 +1856,7 @@
       </c>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:24">
+    <row r="32" spans="1:24" hidden="1">
       <c r="A32" s="1">
         <v>46057</v>
       </c>
@@ -1908,7 +1909,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:24">
+    <row r="33" spans="1:24" hidden="1">
       <c r="A33" s="1">
         <v>46058</v>
       </c>
@@ -1959,7 +1960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24">
+    <row r="34" spans="1:24" hidden="1">
       <c r="A34" s="1">
         <v>46058</v>
       </c>
@@ -2025,7 +2026,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24">
+    <row r="35" spans="1:24" hidden="1">
       <c r="A35" s="1">
         <v>46059</v>
       </c>
@@ -2076,7 +2077,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24">
+    <row r="36" spans="1:24" hidden="1">
       <c r="A36" s="1">
         <v>46059</v>
       </c>
@@ -2127,7 +2128,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24">
+    <row r="37" spans="1:24" hidden="1">
       <c r="A37" s="1">
         <v>46060</v>
       </c>
@@ -2178,7 +2179,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24">
+    <row r="38" spans="1:24" hidden="1">
       <c r="A38" s="1">
         <v>46061</v>
       </c>
@@ -2231,7 +2232,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:24">
+    <row r="39" spans="1:24" hidden="1">
       <c r="A39" s="1">
         <v>46062</v>
       </c>
@@ -2284,7 +2285,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:24">
+    <row r="40" spans="1:24" hidden="1">
       <c r="A40" s="1">
         <v>46063</v>
       </c>
@@ -2543,7 +2544,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:24">
+    <row r="45" spans="1:24" hidden="1">
       <c r="A45" s="1">
         <v>46066</v>
       </c>
@@ -2596,7 +2597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24">
+    <row r="46" spans="1:24" hidden="1">
       <c r="A46" s="1">
         <v>46066</v>
       </c>
@@ -2649,7 +2650,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24">
+    <row r="47" spans="1:24" hidden="1">
       <c r="A47" s="1">
         <v>46067</v>
       </c>
@@ -2784,7 +2785,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" hidden="1">
       <c r="A50" s="1">
         <v>46068</v>
       </c>
@@ -2822,7 +2823,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" hidden="1">
       <c r="A51" s="1">
         <v>46068</v>
       </c>
@@ -2860,7 +2861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" hidden="1">
       <c r="A52" s="1">
         <v>46068</v>
       </c>
@@ -2898,7 +2899,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" hidden="1">
       <c r="A53" s="1">
         <v>46068</v>
       </c>
@@ -3103,7 +3104,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" hidden="1">
       <c r="A58" s="1">
         <v>46074</v>
       </c>
@@ -3147,7 +3148,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" hidden="1">
       <c r="A59" s="1">
         <v>46075</v>
       </c>
@@ -3197,7 +3198,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" hidden="1">
       <c r="A60" s="1">
         <v>46075</v>
       </c>
@@ -3247,7 +3248,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" hidden="1">
       <c r="A61" s="1">
         <v>46076</v>
       </c>
@@ -3297,7 +3298,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" hidden="1">
       <c r="A62" s="1">
         <v>46076</v>
       </c>
@@ -3347,7 +3348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" hidden="1">
       <c r="A63" s="1">
         <v>46077</v>
       </c>
@@ -3397,7 +3398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" hidden="1">
       <c r="A64" s="1">
         <v>46078</v>
       </c>
@@ -3447,7 +3448,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" hidden="1">
       <c r="A65" s="1">
         <v>46078</v>
       </c>
@@ -3497,7 +3498,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" hidden="1">
       <c r="A66" s="1">
         <v>46080</v>
       </c>
@@ -3547,7 +3548,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" hidden="1">
       <c r="A67" s="1">
         <v>46080</v>
       </c>
@@ -3597,7 +3598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" hidden="1">
       <c r="A68" s="1">
         <v>46080</v>
       </c>
@@ -3635,7 +3636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" hidden="1">
       <c r="A69" s="1">
         <v>46080</v>
       </c>
@@ -3673,7 +3674,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" hidden="1">
       <c r="A70" s="1">
         <v>46080</v>
       </c>
@@ -3711,7 +3712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" hidden="1">
       <c r="A71" s="1">
         <v>46081</v>
       </c>
@@ -3752,7 +3753,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" hidden="1">
       <c r="A72" s="1">
         <v>46081</v>
       </c>
@@ -3793,7 +3794,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" hidden="1">
       <c r="A73" s="1">
         <v>46082</v>
       </c>
@@ -3846,7 +3847,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" hidden="1">
       <c r="A74" s="1">
         <v>46082</v>
       </c>
@@ -3887,7 +3888,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" hidden="1">
       <c r="A75" s="1">
         <v>46083</v>
       </c>
@@ -3928,7 +3929,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" hidden="1">
       <c r="A76" s="1">
         <v>46084</v>
       </c>
@@ -3969,7 +3970,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" hidden="1">
       <c r="A77" s="1">
         <v>46084</v>
       </c>
@@ -4104,7 +4105,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" hidden="1">
       <c r="A80" s="1">
         <v>46087</v>
       </c>
@@ -4157,7 +4158,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" hidden="1">
       <c r="A81" s="1">
         <v>46087</v>
       </c>
@@ -4210,7 +4211,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" hidden="1">
       <c r="A82" s="1">
         <v>46088</v>
       </c>
@@ -4263,7 +4264,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" hidden="1">
       <c r="A83" s="1">
         <v>46089</v>
       </c>
@@ -4316,7 +4317,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" hidden="1">
       <c r="A84" s="1">
         <v>46090</v>
       </c>
@@ -4369,7 +4370,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" hidden="1">
       <c r="A85" s="1">
         <v>46091</v>
       </c>
@@ -4422,7 +4423,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" hidden="1">
       <c r="A86" s="1">
         <v>46092</v>
       </c>
@@ -4475,7 +4476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" hidden="1">
       <c r="A87" s="1">
         <v>46094</v>
       </c>
@@ -4528,7 +4529,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" hidden="1">
       <c r="A88" s="1">
         <v>46094</v>
       </c>
@@ -4581,7 +4582,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" hidden="1">
       <c r="A89" s="1">
         <v>46096</v>
       </c>
@@ -4634,7 +4635,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" hidden="1">
       <c r="A90" s="1">
         <v>46096</v>
       </c>
@@ -4687,7 +4688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" hidden="1">
       <c r="A91" s="1">
         <v>46097</v>
       </c>
@@ -4740,7 +4741,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" hidden="1">
       <c r="A92" s="1">
         <v>46098</v>
       </c>
@@ -4793,7 +4794,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" hidden="1">
       <c r="A93" s="1">
         <v>46098</v>
       </c>
@@ -4846,7 +4847,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" hidden="1">
       <c r="A94" s="1">
         <v>46099</v>
       </c>
@@ -4966,7 +4967,7 @@
       </c>
       <c r="R96" s="1"/>
     </row>
-    <row r="97" spans="1:19">
+    <row r="97" spans="1:19" hidden="1">
       <c r="A97" s="1">
         <v>46102</v>
       </c>
@@ -5013,7 +5014,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="1:19">
+    <row r="98" spans="1:19" hidden="1">
       <c r="A98" s="1">
         <v>46102</v>
       </c>
@@ -5063,7 +5064,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="99" spans="1:19">
+    <row r="99" spans="1:19" hidden="1">
       <c r="A99" s="1">
         <v>46103</v>
       </c>
@@ -5113,7 +5114,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="100" spans="1:19">
+    <row r="100" spans="1:19" hidden="1">
       <c r="A100" s="1">
         <v>46104</v>
       </c>
@@ -5252,7 +5253,7 @@
       </c>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:19" hidden="1">
       <c r="A103" s="1">
         <v>46111</v>
       </c>
@@ -5302,7 +5303,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="1:19">
+    <row r="104" spans="1:19" hidden="1">
       <c r="A104" s="1">
         <v>46112</v>
       </c>
@@ -5349,7 +5350,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="105" spans="1:19">
+    <row r="105" spans="1:19" hidden="1">
       <c r="A105" s="1">
         <v>46113</v>
       </c>
@@ -5399,7 +5400,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:19" hidden="1">
       <c r="A106" s="1">
         <v>46115</v>
       </c>
@@ -5449,7 +5450,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="107" spans="1:19">
+    <row r="107" spans="1:19" hidden="1">
       <c r="A107" s="1">
         <v>46116</v>
       </c>
@@ -5638,7 +5639,7 @@
       </c>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:19">
+    <row r="111" spans="1:19" hidden="1">
       <c r="A111" s="1">
         <v>46124</v>
       </c>
@@ -5662,7 +5663,7 @@
       </c>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" spans="1:19">
+    <row r="112" spans="1:19" hidden="1">
       <c r="A112" s="1">
         <v>46124</v>
       </c>
@@ -5686,7 +5687,7 @@
       </c>
       <c r="R112" s="1"/>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" hidden="1">
       <c r="A113" s="1">
         <v>46124</v>
       </c>
@@ -5710,7 +5711,7 @@
       </c>
       <c r="R113" s="1"/>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" hidden="1">
       <c r="A114" s="1">
         <v>46124</v>
       </c>
@@ -5734,7 +5735,7 @@
       </c>
       <c r="R114" s="1"/>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" hidden="1">
       <c r="A115" s="1">
         <v>46124</v>
       </c>
@@ -5758,7 +5759,7 @@
       </c>
       <c r="R115" s="1"/>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" hidden="1">
       <c r="A116" s="1">
         <v>46124</v>
       </c>
@@ -5782,7 +5783,7 @@
       </c>
       <c r="R116" s="1"/>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" hidden="1">
       <c r="A117" s="1">
         <v>46125</v>
       </c>
@@ -5832,7 +5833,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" hidden="1">
       <c r="A118" s="1">
         <v>46126</v>
       </c>
@@ -5971,7 +5972,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" hidden="1">
       <c r="A121" s="1">
         <v>46132</v>
       </c>
@@ -6021,7 +6022,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="122" spans="1:19">
+    <row r="122" spans="1:19" hidden="1">
       <c r="A122" s="1">
         <v>46134</v>
       </c>
@@ -6071,7 +6072,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="123" spans="1:19">
+    <row r="123" spans="1:19" hidden="1">
       <c r="A123" s="1">
         <v>46136</v>
       </c>
@@ -6121,7 +6122,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:19">
+    <row r="124" spans="1:19" hidden="1">
       <c r="A124" s="1">
         <v>46136</v>
       </c>
@@ -6171,7 +6172,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="125" spans="1:19">
+    <row r="125" spans="1:19" hidden="1">
       <c r="A125" s="1">
         <v>46137</v>
       </c>
@@ -6277,7 +6278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:19">
+    <row r="127" spans="1:19" hidden="1">
       <c r="A127" s="1">
         <v>46138</v>
       </c>
@@ -6330,7 +6331,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:19">
+    <row r="128" spans="1:19" hidden="1">
       <c r="A128" s="1">
         <v>46139</v>
       </c>
@@ -6383,7 +6384,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:24" hidden="1">
       <c r="A129" s="1">
         <v>46140</v>
       </c>
@@ -6517,7 +6518,7 @@
       </c>
       <c r="R131" s="1"/>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:24" hidden="1">
       <c r="A132" s="1">
         <v>46142</v>
       </c>
@@ -6565,7 +6566,7 @@
       </c>
       <c r="R132" s="1"/>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:24" hidden="1">
       <c r="A133" s="1">
         <v>46142</v>
       </c>
@@ -6830,7 +6831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" spans="1:24" hidden="1">
       <c r="A138" s="1">
         <v>46147</v>
       </c>
@@ -6880,7 +6881,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:24">
+    <row r="139" spans="1:24" hidden="1">
       <c r="A139" s="1">
         <v>46147</v>
       </c>
@@ -6930,7 +6931,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:24">
+    <row r="140" spans="1:24" hidden="1">
       <c r="A140" s="1">
         <v>46149</v>
       </c>
@@ -6983,7 +6984,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:24">
+    <row r="141" spans="1:24" hidden="1">
       <c r="A141" s="1">
         <v>46150</v>
       </c>
@@ -7031,7 +7032,7 @@
       </c>
       <c r="R141" s="1"/>
     </row>
-    <row r="142" spans="1:24">
+    <row r="142" spans="1:24" hidden="1">
       <c r="A142" s="1">
         <v>46151</v>
       </c>
@@ -7084,7 +7085,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="143" spans="1:24">
+    <row r="143" spans="1:24" hidden="1">
       <c r="A143" s="1">
         <v>46152</v>
       </c>
@@ -7149,7 +7150,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="144" spans="1:24">
+    <row r="144" spans="1:24" hidden="1">
       <c r="A144" s="1">
         <v>46152</v>
       </c>
@@ -7196,7 +7197,7 @@
       <c r="T144" s="1"/>
       <c r="W144" s="1"/>
     </row>
-    <row r="145" spans="1:22">
+    <row r="145" spans="1:22" hidden="1">
       <c r="A145" s="1">
         <v>46153</v>
       </c>
@@ -7252,7 +7253,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="146" spans="1:22">
+    <row r="146" spans="1:22" hidden="1">
       <c r="A146" s="1">
         <v>46154</v>
       </c>
@@ -7414,7 +7415,7 @@
       </c>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:22">
+    <row r="150" spans="1:22" hidden="1">
       <c r="A150" s="1">
         <v>46160</v>
       </c>
@@ -7461,7 +7462,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="151" spans="1:22">
+    <row r="151" spans="1:22" hidden="1">
       <c r="A151" s="1">
         <v>46161</v>
       </c>
@@ -7586,7 +7587,7 @@
       </c>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:22">
+    <row r="154" spans="1:22" hidden="1">
       <c r="A154" s="1">
         <v>46168</v>
       </c>
@@ -7631,7 +7632,7 @@
       </c>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:22">
+    <row r="155" spans="1:22" hidden="1">
       <c r="A155" s="1">
         <v>46170</v>
       </c>
@@ -8230,7 +8231,7 @@
       </c>
       <c r="R167" s="1"/>
     </row>
-    <row r="168" spans="1:18">
+    <row r="168" spans="1:18" hidden="1">
       <c r="A168" s="1">
         <v>46179</v>
       </c>
@@ -8275,7 +8276,7 @@
       </c>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18">
+    <row r="169" spans="1:18" hidden="1">
       <c r="A169" s="1">
         <v>46179</v>
       </c>
@@ -8587,7 +8588,7 @@
       </c>
       <c r="R175" s="1"/>
     </row>
-    <row r="176" spans="1:18">
+    <row r="176" spans="1:18" hidden="1">
       <c r="A176" s="1">
         <v>46186</v>
       </c>
@@ -8623,7 +8624,7 @@
       </c>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18">
+    <row r="177" spans="1:18" hidden="1">
       <c r="A177" s="1">
         <v>46187</v>
       </c>
@@ -8668,7 +8669,7 @@
       </c>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:18">
+    <row r="178" spans="1:18" hidden="1">
       <c r="A178" s="1">
         <v>46187</v>
       </c>
@@ -8720,6 +8721,9 @@
       <c r="F179" t="s">
         <v>19</v>
       </c>
+      <c r="G179">
+        <v>21</v>
+      </c>
       <c r="I179">
         <v>925</v>
       </c>
@@ -8783,31 +8787,243 @@
       <c r="R180" s="1"/>
     </row>
     <row r="181" spans="1:18">
-      <c r="A181" s="1"/>
+      <c r="A181" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B181">
+        <v>279</v>
+      </c>
+      <c r="C181">
+        <v>6800</v>
+      </c>
+      <c r="D181">
+        <v>6720</v>
+      </c>
+      <c r="E181">
+        <v>57</v>
+      </c>
+      <c r="F181" t="s">
+        <v>19</v>
+      </c>
+      <c r="G181">
+        <v>31</v>
+      </c>
+      <c r="I181">
+        <v>925</v>
+      </c>
+      <c r="K181">
+        <v>10</v>
+      </c>
+      <c r="L181">
+        <v>672</v>
+      </c>
+      <c r="O181" s="1">
+        <v>46193</v>
+      </c>
+      <c r="P181" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q181">
+        <v>18</v>
+      </c>
       <c r="R181" s="1"/>
     </row>
     <row r="182" spans="1:18">
-      <c r="A182" s="1"/>
+      <c r="A182" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B182">
+        <v>280</v>
+      </c>
+      <c r="C182">
+        <v>6800</v>
+      </c>
+      <c r="D182">
+        <v>6720</v>
+      </c>
+      <c r="E182">
+        <v>57</v>
+      </c>
+      <c r="F182" t="s">
+        <v>19</v>
+      </c>
+      <c r="G182">
+        <v>45</v>
+      </c>
+      <c r="I182">
+        <v>925</v>
+      </c>
+      <c r="K182">
+        <v>10</v>
+      </c>
+      <c r="L182">
+        <v>672</v>
+      </c>
       <c r="R182" s="1"/>
     </row>
     <row r="183" spans="1:18">
-      <c r="A183" s="1"/>
+      <c r="A183" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B183">
+        <v>281</v>
+      </c>
+      <c r="C183">
+        <v>6800</v>
+      </c>
+      <c r="D183">
+        <v>6720</v>
+      </c>
+      <c r="E183">
+        <v>57</v>
+      </c>
+      <c r="F183" t="s">
+        <v>19</v>
+      </c>
+      <c r="G183">
+        <v>50</v>
+      </c>
+      <c r="I183">
+        <v>925</v>
+      </c>
+      <c r="K183">
+        <v>10</v>
+      </c>
+      <c r="L183">
+        <v>672</v>
+      </c>
       <c r="R183" s="1"/>
     </row>
     <row r="184" spans="1:18">
-      <c r="A184" s="1"/>
+      <c r="A184" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B184">
+        <v>282</v>
+      </c>
+      <c r="C184">
+        <v>6800</v>
+      </c>
+      <c r="D184">
+        <v>6720</v>
+      </c>
+      <c r="E184">
+        <v>57</v>
+      </c>
+      <c r="F184" t="s">
+        <v>19</v>
+      </c>
+      <c r="G184">
+        <v>29</v>
+      </c>
+      <c r="I184">
+        <v>925</v>
+      </c>
+      <c r="K184">
+        <v>10</v>
+      </c>
+      <c r="L184">
+        <v>672</v>
+      </c>
       <c r="R184" s="1"/>
     </row>
     <row r="185" spans="1:18">
-      <c r="A185" s="1"/>
+      <c r="A185" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B185">
+        <v>283</v>
+      </c>
+      <c r="C185">
+        <v>6800</v>
+      </c>
+      <c r="D185">
+        <v>6720</v>
+      </c>
+      <c r="E185">
+        <v>57</v>
+      </c>
+      <c r="F185" t="s">
+        <v>19</v>
+      </c>
+      <c r="G185">
+        <v>53</v>
+      </c>
+      <c r="I185">
+        <v>925</v>
+      </c>
+      <c r="K185">
+        <v>10</v>
+      </c>
+      <c r="L185">
+        <v>672</v>
+      </c>
       <c r="R185" s="1"/>
     </row>
     <row r="186" spans="1:18">
-      <c r="A186" s="1"/>
+      <c r="A186" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B186">
+        <v>284</v>
+      </c>
+      <c r="C186">
+        <v>6800</v>
+      </c>
+      <c r="D186">
+        <v>6720</v>
+      </c>
+      <c r="E186">
+        <v>57</v>
+      </c>
+      <c r="F186" t="s">
+        <v>19</v>
+      </c>
+      <c r="G186">
+        <v>25</v>
+      </c>
+      <c r="I186">
+        <v>925</v>
+      </c>
+      <c r="K186">
+        <v>10</v>
+      </c>
+      <c r="L186">
+        <v>672</v>
+      </c>
       <c r="R186" s="1"/>
     </row>
     <row r="187" spans="1:18">
-      <c r="A187" s="1"/>
+      <c r="A187" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B187">
+        <v>285</v>
+      </c>
+      <c r="C187">
+        <v>6800</v>
+      </c>
+      <c r="D187">
+        <v>6720</v>
+      </c>
+      <c r="E187">
+        <v>57</v>
+      </c>
+      <c r="F187" t="s">
+        <v>19</v>
+      </c>
+      <c r="G187">
+        <v>11</v>
+      </c>
+      <c r="I187">
+        <v>925</v>
+      </c>
+      <c r="K187">
+        <v>10</v>
+      </c>
+      <c r="L187">
+        <v>672</v>
+      </c>
       <c r="R187" s="1"/>
     </row>
     <row r="188" spans="1:18">
@@ -8989,8 +9205,12 @@
       <c r="A235" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X180">
-    <filterColumn colId="5"/>
+  <autoFilter ref="A1:X187">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="PURE GOLD"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="13"/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -6564,7 +6564,12 @@
       <c r="Q132">
         <v>11</v>
       </c>
-      <c r="R132" s="1"/>
+      <c r="R132" s="1">
+        <v>46195</v>
+      </c>
+      <c r="S132" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="133" spans="1:24" hidden="1">
       <c r="A133" s="1">
@@ -7030,7 +7035,12 @@
       <c r="Q141">
         <v>4</v>
       </c>
-      <c r="R141" s="1"/>
+      <c r="R141" s="1">
+        <v>46194</v>
+      </c>
+      <c r="S141" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="142" spans="1:24" hidden="1">
       <c r="A142" s="1">
@@ -8859,6 +8869,15 @@
       <c r="L182">
         <v>672</v>
       </c>
+      <c r="O182" s="1">
+        <v>46193</v>
+      </c>
+      <c r="P182" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q182">
+        <v>6</v>
+      </c>
       <c r="R182" s="1"/>
     </row>
     <row r="183" spans="1:18">
@@ -8925,6 +8944,15 @@
       <c r="L184">
         <v>672</v>
       </c>
+      <c r="O184" s="1">
+        <v>46195</v>
+      </c>
+      <c r="P184" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q184">
+        <v>11</v>
+      </c>
       <c r="R184" s="1"/>
     </row>
     <row r="185" spans="1:18">
@@ -8957,6 +8985,15 @@
       </c>
       <c r="L185">
         <v>672</v>
+      </c>
+      <c r="O185" s="1">
+        <v>46195</v>
+      </c>
+      <c r="P185" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q185">
+        <v>4</v>
       </c>
       <c r="R185" s="1"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -7780,7 +7780,12 @@
       <c r="Q157">
         <v>10</v>
       </c>
-      <c r="R157" s="1"/>
+      <c r="R157" s="1">
+        <v>46196</v>
+      </c>
+      <c r="S157" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="158" spans="1:22">
       <c r="A158" s="1">
@@ -9027,6 +9032,15 @@
       </c>
       <c r="L186">
         <v>672</v>
+      </c>
+      <c r="O186" s="1">
+        <v>46197</v>
+      </c>
+      <c r="P186" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q186">
+        <v>10</v>
       </c>
       <c r="R186" s="1"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$195</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -542,7 +542,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:X235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -637,7 +636,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="2" customFormat="1" ht="15" hidden="1" customHeight="1">
+    <row r="2" spans="1:24" s="2" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="6">
         <v>45976</v>
       </c>
@@ -675,7 +674,7 @@
       <c r="V2" s="7"/>
       <c r="X2" s="5"/>
     </row>
-    <row r="3" spans="1:24" hidden="1">
+    <row r="3" spans="1:24">
       <c r="A3" s="1">
         <v>46022</v>
       </c>
@@ -724,7 +723,7 @@
       </c>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:24" hidden="1">
+    <row r="4" spans="1:24">
       <c r="A4" s="1">
         <v>46027</v>
       </c>
@@ -761,7 +760,7 @@
       </c>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:24" hidden="1">
+    <row r="5" spans="1:24">
       <c r="A5" s="1">
         <v>46028</v>
       </c>
@@ -798,7 +797,7 @@
       </c>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:24" hidden="1">
+    <row r="6" spans="1:24">
       <c r="A6" s="1">
         <v>46031</v>
       </c>
@@ -835,7 +834,7 @@
       </c>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:24" hidden="1">
+    <row r="7" spans="1:24">
       <c r="A7" s="1">
         <v>46031</v>
       </c>
@@ -872,7 +871,7 @@
       </c>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:24" hidden="1">
+    <row r="8" spans="1:24">
       <c r="A8" s="1">
         <v>46032</v>
       </c>
@@ -911,7 +910,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:24" hidden="1">
+    <row r="9" spans="1:24">
       <c r="A9" s="1">
         <v>46033</v>
       </c>
@@ -948,7 +947,7 @@
       </c>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:24" hidden="1">
+    <row r="10" spans="1:24">
       <c r="A10" s="1">
         <v>46034</v>
       </c>
@@ -985,7 +984,7 @@
       </c>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:24" hidden="1">
+    <row r="11" spans="1:24">
       <c r="A11" s="1">
         <v>46035</v>
       </c>
@@ -1022,7 +1021,7 @@
       </c>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:24" hidden="1">
+    <row r="12" spans="1:24">
       <c r="A12" s="1">
         <v>46035</v>
       </c>
@@ -1064,7 +1063,7 @@
       <c r="U12" s="4"/>
       <c r="V12" s="9"/>
     </row>
-    <row r="13" spans="1:24" hidden="1">
+    <row r="13" spans="1:24">
       <c r="A13" s="1">
         <v>46036</v>
       </c>
@@ -1106,7 +1105,7 @@
       <c r="U13" s="4"/>
       <c r="V13" s="9"/>
     </row>
-    <row r="14" spans="1:24" hidden="1">
+    <row r="14" spans="1:24">
       <c r="A14" s="1">
         <v>46040</v>
       </c>
@@ -1143,7 +1142,7 @@
       <c r="U14" s="4"/>
       <c r="V14" s="9"/>
     </row>
-    <row r="15" spans="1:24" hidden="1">
+    <row r="15" spans="1:24">
       <c r="A15" s="1">
         <v>46041</v>
       </c>
@@ -1182,7 +1181,7 @@
       <c r="U15" s="4"/>
       <c r="V15" s="9"/>
     </row>
-    <row r="16" spans="1:24" hidden="1">
+    <row r="16" spans="1:24">
       <c r="A16" s="1">
         <v>46042</v>
       </c>
@@ -1221,7 +1220,7 @@
       <c r="U16" s="4"/>
       <c r="V16" s="9"/>
     </row>
-    <row r="17" spans="1:24" hidden="1">
+    <row r="17" spans="1:24">
       <c r="A17" s="1">
         <v>46044</v>
       </c>
@@ -1272,7 +1271,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:24" hidden="1">
+    <row r="18" spans="1:24">
       <c r="A18" s="1">
         <v>46044</v>
       </c>
@@ -1308,7 +1307,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" hidden="1">
+    <row r="19" spans="1:24">
       <c r="A19" s="1">
         <v>46046</v>
       </c>
@@ -1344,7 +1343,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:24" hidden="1">
+    <row r="20" spans="1:24">
       <c r="A20" s="1">
         <v>46047</v>
       </c>
@@ -1380,7 +1379,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:24" hidden="1">
+    <row r="21" spans="1:24">
       <c r="A21" s="1">
         <v>46047</v>
       </c>
@@ -1416,7 +1415,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:24" hidden="1">
+    <row r="22" spans="1:24">
       <c r="A22" s="1">
         <v>46050</v>
       </c>
@@ -1469,7 +1468,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:24" hidden="1">
+    <row r="23" spans="1:24">
       <c r="A23" s="1">
         <v>46050</v>
       </c>
@@ -1505,7 +1504,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="24" spans="1:24" hidden="1">
+    <row r="24" spans="1:24">
       <c r="A24" s="1">
         <v>46051</v>
       </c>
@@ -1546,7 +1545,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:24" hidden="1">
+    <row r="25" spans="1:24">
       <c r="A25" s="1">
         <v>46051</v>
       </c>
@@ -1582,7 +1581,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:24" hidden="1">
+    <row r="26" spans="1:24">
       <c r="A26" s="1">
         <v>46052</v>
       </c>
@@ -1618,7 +1617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:24" hidden="1">
+    <row r="27" spans="1:24">
       <c r="A27" s="1">
         <v>46052</v>
       </c>
@@ -1654,7 +1653,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" hidden="1">
+    <row r="28" spans="1:24">
       <c r="A28" s="1">
         <v>46053</v>
       </c>
@@ -1690,7 +1689,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" hidden="1">
+    <row r="29" spans="1:24">
       <c r="A29" s="1">
         <v>46053</v>
       </c>
@@ -1741,7 +1740,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:24" hidden="1">
+    <row r="30" spans="1:24">
       <c r="A30" s="1">
         <v>46053</v>
       </c>
@@ -1856,7 +1855,7 @@
       </c>
       <c r="S31" s="1"/>
     </row>
-    <row r="32" spans="1:24" hidden="1">
+    <row r="32" spans="1:24">
       <c r="A32" s="1">
         <v>46057</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="33" spans="1:24" hidden="1">
+    <row r="33" spans="1:24">
       <c r="A33" s="1">
         <v>46058</v>
       </c>
@@ -1960,7 +1959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" hidden="1">
+    <row r="34" spans="1:24">
       <c r="A34" s="1">
         <v>46058</v>
       </c>
@@ -2026,7 +2025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" hidden="1">
+    <row r="35" spans="1:24">
       <c r="A35" s="1">
         <v>46059</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" hidden="1">
+    <row r="36" spans="1:24">
       <c r="A36" s="1">
         <v>46059</v>
       </c>
@@ -2128,7 +2127,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" hidden="1">
+    <row r="37" spans="1:24">
       <c r="A37" s="1">
         <v>46060</v>
       </c>
@@ -2179,7 +2178,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" hidden="1">
+    <row r="38" spans="1:24">
       <c r="A38" s="1">
         <v>46061</v>
       </c>
@@ -2232,7 +2231,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="1:24" hidden="1">
+    <row r="39" spans="1:24">
       <c r="A39" s="1">
         <v>46062</v>
       </c>
@@ -2285,7 +2284,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="40" spans="1:24" hidden="1">
+    <row r="40" spans="1:24">
       <c r="A40" s="1">
         <v>46063</v>
       </c>
@@ -2544,7 +2543,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" spans="1:24" hidden="1">
+    <row r="45" spans="1:24">
       <c r="A45" s="1">
         <v>46066</v>
       </c>
@@ -2597,7 +2596,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" hidden="1">
+    <row r="46" spans="1:24">
       <c r="A46" s="1">
         <v>46066</v>
       </c>
@@ -2650,7 +2649,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" hidden="1">
+    <row r="47" spans="1:24">
       <c r="A47" s="1">
         <v>46067</v>
       </c>
@@ -2785,7 +2784,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="50" spans="1:19" hidden="1">
+    <row r="50" spans="1:19">
       <c r="A50" s="1">
         <v>46068</v>
       </c>
@@ -2823,7 +2822,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" spans="1:19" hidden="1">
+    <row r="51" spans="1:19">
       <c r="A51" s="1">
         <v>46068</v>
       </c>
@@ -2861,7 +2860,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="1:19" hidden="1">
+    <row r="52" spans="1:19">
       <c r="A52" s="1">
         <v>46068</v>
       </c>
@@ -2899,7 +2898,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1">
+    <row r="53" spans="1:19">
       <c r="A53" s="1">
         <v>46068</v>
       </c>
@@ -3104,7 +3103,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" spans="1:19" hidden="1">
+    <row r="58" spans="1:19">
       <c r="A58" s="1">
         <v>46074</v>
       </c>
@@ -3148,7 +3147,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="59" spans="1:19" hidden="1">
+    <row r="59" spans="1:19">
       <c r="A59" s="1">
         <v>46075</v>
       </c>
@@ -3198,7 +3197,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" spans="1:19" hidden="1">
+    <row r="60" spans="1:19">
       <c r="A60" s="1">
         <v>46075</v>
       </c>
@@ -3248,7 +3247,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="61" spans="1:19" hidden="1">
+    <row r="61" spans="1:19">
       <c r="A61" s="1">
         <v>46076</v>
       </c>
@@ -3298,7 +3297,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:19" hidden="1">
+    <row r="62" spans="1:19">
       <c r="A62" s="1">
         <v>46076</v>
       </c>
@@ -3348,7 +3347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:19" hidden="1">
+    <row r="63" spans="1:19">
       <c r="A63" s="1">
         <v>46077</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:19" hidden="1">
+    <row r="64" spans="1:19">
       <c r="A64" s="1">
         <v>46078</v>
       </c>
@@ -3448,7 +3447,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="65" spans="1:19" hidden="1">
+    <row r="65" spans="1:19">
       <c r="A65" s="1">
         <v>46078</v>
       </c>
@@ -3498,7 +3497,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="66" spans="1:19" hidden="1">
+    <row r="66" spans="1:19">
       <c r="A66" s="1">
         <v>46080</v>
       </c>
@@ -3548,7 +3547,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="67" spans="1:19" hidden="1">
+    <row r="67" spans="1:19">
       <c r="A67" s="1">
         <v>46080</v>
       </c>
@@ -3598,7 +3597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:19" hidden="1">
+    <row r="68" spans="1:19">
       <c r="A68" s="1">
         <v>46080</v>
       </c>
@@ -3636,7 +3635,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:19" hidden="1">
+    <row r="69" spans="1:19">
       <c r="A69" s="1">
         <v>46080</v>
       </c>
@@ -3674,7 +3673,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="70" spans="1:19" hidden="1">
+    <row r="70" spans="1:19">
       <c r="A70" s="1">
         <v>46080</v>
       </c>
@@ -3712,7 +3711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:19" hidden="1">
+    <row r="71" spans="1:19">
       <c r="A71" s="1">
         <v>46081</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="72" spans="1:19" hidden="1">
+    <row r="72" spans="1:19">
       <c r="A72" s="1">
         <v>46081</v>
       </c>
@@ -3794,7 +3793,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="73" spans="1:19" hidden="1">
+    <row r="73" spans="1:19">
       <c r="A73" s="1">
         <v>46082</v>
       </c>
@@ -3847,7 +3846,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:19" hidden="1">
+    <row r="74" spans="1:19">
       <c r="A74" s="1">
         <v>46082</v>
       </c>
@@ -3888,7 +3887,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="75" spans="1:19" hidden="1">
+    <row r="75" spans="1:19">
       <c r="A75" s="1">
         <v>46083</v>
       </c>
@@ -3929,7 +3928,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1">
+    <row r="76" spans="1:19">
       <c r="A76" s="1">
         <v>46084</v>
       </c>
@@ -3970,7 +3969,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:19" hidden="1">
+    <row r="77" spans="1:19">
       <c r="A77" s="1">
         <v>46084</v>
       </c>
@@ -4105,7 +4104,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1">
+    <row r="80" spans="1:19">
       <c r="A80" s="1">
         <v>46087</v>
       </c>
@@ -4158,7 +4157,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="81" spans="1:19" hidden="1">
+    <row r="81" spans="1:19">
       <c r="A81" s="1">
         <v>46087</v>
       </c>
@@ -4211,7 +4210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:19" hidden="1">
+    <row r="82" spans="1:19">
       <c r="A82" s="1">
         <v>46088</v>
       </c>
@@ -4264,7 +4263,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="1:19" hidden="1">
+    <row r="83" spans="1:19">
       <c r="A83" s="1">
         <v>46089</v>
       </c>
@@ -4317,7 +4316,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="84" spans="1:19" hidden="1">
+    <row r="84" spans="1:19">
       <c r="A84" s="1">
         <v>46090</v>
       </c>
@@ -4370,7 +4369,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" spans="1:19" hidden="1">
+    <row r="85" spans="1:19">
       <c r="A85" s="1">
         <v>46091</v>
       </c>
@@ -4423,7 +4422,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1">
+    <row r="86" spans="1:19">
       <c r="A86" s="1">
         <v>46092</v>
       </c>
@@ -4476,7 +4475,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:19" hidden="1">
+    <row r="87" spans="1:19">
       <c r="A87" s="1">
         <v>46094</v>
       </c>
@@ -4529,7 +4528,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" spans="1:19" hidden="1">
+    <row r="88" spans="1:19">
       <c r="A88" s="1">
         <v>46094</v>
       </c>
@@ -4582,7 +4581,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="89" spans="1:19" hidden="1">
+    <row r="89" spans="1:19">
       <c r="A89" s="1">
         <v>46096</v>
       </c>
@@ -4635,7 +4634,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="90" spans="1:19" hidden="1">
+    <row r="90" spans="1:19">
       <c r="A90" s="1">
         <v>46096</v>
       </c>
@@ -4688,7 +4687,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:19" hidden="1">
+    <row r="91" spans="1:19">
       <c r="A91" s="1">
         <v>46097</v>
       </c>
@@ -4741,7 +4740,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="1:19" hidden="1">
+    <row r="92" spans="1:19">
       <c r="A92" s="1">
         <v>46098</v>
       </c>
@@ -4794,7 +4793,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="93" spans="1:19" hidden="1">
+    <row r="93" spans="1:19">
       <c r="A93" s="1">
         <v>46098</v>
       </c>
@@ -4847,7 +4846,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" spans="1:19" hidden="1">
+    <row r="94" spans="1:19">
       <c r="A94" s="1">
         <v>46099</v>
       </c>
@@ -4967,7 +4966,7 @@
       </c>
       <c r="R96" s="1"/>
     </row>
-    <row r="97" spans="1:19" hidden="1">
+    <row r="97" spans="1:19">
       <c r="A97" s="1">
         <v>46102</v>
       </c>
@@ -5014,7 +5013,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="98" spans="1:19" hidden="1">
+    <row r="98" spans="1:19">
       <c r="A98" s="1">
         <v>46102</v>
       </c>
@@ -5064,7 +5063,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="99" spans="1:19" hidden="1">
+    <row r="99" spans="1:19">
       <c r="A99" s="1">
         <v>46103</v>
       </c>
@@ -5114,7 +5113,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="100" spans="1:19" hidden="1">
+    <row r="100" spans="1:19">
       <c r="A100" s="1">
         <v>46104</v>
       </c>
@@ -5253,7 +5252,7 @@
       </c>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" spans="1:19" hidden="1">
+    <row r="103" spans="1:19">
       <c r="A103" s="1">
         <v>46111</v>
       </c>
@@ -5303,7 +5302,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="1:19" hidden="1">
+    <row r="104" spans="1:19">
       <c r="A104" s="1">
         <v>46112</v>
       </c>
@@ -5350,7 +5349,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1">
+    <row r="105" spans="1:19">
       <c r="A105" s="1">
         <v>46113</v>
       </c>
@@ -5400,7 +5399,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="106" spans="1:19" hidden="1">
+    <row r="106" spans="1:19">
       <c r="A106" s="1">
         <v>46115</v>
       </c>
@@ -5450,7 +5449,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="107" spans="1:19" hidden="1">
+    <row r="107" spans="1:19">
       <c r="A107" s="1">
         <v>46116</v>
       </c>
@@ -5639,7 +5638,7 @@
       </c>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" spans="1:19" hidden="1">
+    <row r="111" spans="1:19">
       <c r="A111" s="1">
         <v>46124</v>
       </c>
@@ -5663,7 +5662,7 @@
       </c>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" spans="1:19" hidden="1">
+    <row r="112" spans="1:19">
       <c r="A112" s="1">
         <v>46124</v>
       </c>
@@ -5687,7 +5686,7 @@
       </c>
       <c r="R112" s="1"/>
     </row>
-    <row r="113" spans="1:19" hidden="1">
+    <row r="113" spans="1:19">
       <c r="A113" s="1">
         <v>46124</v>
       </c>
@@ -5711,7 +5710,7 @@
       </c>
       <c r="R113" s="1"/>
     </row>
-    <row r="114" spans="1:19" hidden="1">
+    <row r="114" spans="1:19">
       <c r="A114" s="1">
         <v>46124</v>
       </c>
@@ -5735,7 +5734,7 @@
       </c>
       <c r="R114" s="1"/>
     </row>
-    <row r="115" spans="1:19" hidden="1">
+    <row r="115" spans="1:19">
       <c r="A115" s="1">
         <v>46124</v>
       </c>
@@ -5759,7 +5758,7 @@
       </c>
       <c r="R115" s="1"/>
     </row>
-    <row r="116" spans="1:19" hidden="1">
+    <row r="116" spans="1:19">
       <c r="A116" s="1">
         <v>46124</v>
       </c>
@@ -5783,7 +5782,7 @@
       </c>
       <c r="R116" s="1"/>
     </row>
-    <row r="117" spans="1:19" hidden="1">
+    <row r="117" spans="1:19">
       <c r="A117" s="1">
         <v>46125</v>
       </c>
@@ -5833,7 +5832,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1">
+    <row r="118" spans="1:19">
       <c r="A118" s="1">
         <v>46126</v>
       </c>
@@ -5972,7 +5971,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:19" hidden="1">
+    <row r="121" spans="1:19">
       <c r="A121" s="1">
         <v>46132</v>
       </c>
@@ -6022,7 +6021,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1">
+    <row r="122" spans="1:19">
       <c r="A122" s="1">
         <v>46134</v>
       </c>
@@ -6072,7 +6071,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1">
+    <row r="123" spans="1:19">
       <c r="A123" s="1">
         <v>46136</v>
       </c>
@@ -6122,7 +6121,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1">
+    <row r="124" spans="1:19">
       <c r="A124" s="1">
         <v>46136</v>
       </c>
@@ -6172,7 +6171,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="125" spans="1:19" hidden="1">
+    <row r="125" spans="1:19">
       <c r="A125" s="1">
         <v>46137</v>
       </c>
@@ -6278,7 +6277,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:19" hidden="1">
+    <row r="127" spans="1:19">
       <c r="A127" s="1">
         <v>46138</v>
       </c>
@@ -6331,7 +6330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:19" hidden="1">
+    <row r="128" spans="1:19">
       <c r="A128" s="1">
         <v>46139</v>
       </c>
@@ -6384,7 +6383,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="129" spans="1:24" hidden="1">
+    <row r="129" spans="1:24">
       <c r="A129" s="1">
         <v>46140</v>
       </c>
@@ -6518,7 +6517,7 @@
       </c>
       <c r="R131" s="1"/>
     </row>
-    <row r="132" spans="1:24" hidden="1">
+    <row r="132" spans="1:24">
       <c r="A132" s="1">
         <v>46142</v>
       </c>
@@ -6571,7 +6570,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="133" spans="1:24" hidden="1">
+    <row r="133" spans="1:24">
       <c r="A133" s="1">
         <v>46142</v>
       </c>
@@ -6836,7 +6835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:24" hidden="1">
+    <row r="138" spans="1:24">
       <c r="A138" s="1">
         <v>46147</v>
       </c>
@@ -6886,7 +6885,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:24" hidden="1">
+    <row r="139" spans="1:24">
       <c r="A139" s="1">
         <v>46147</v>
       </c>
@@ -6936,7 +6935,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:24" hidden="1">
+    <row r="140" spans="1:24">
       <c r="A140" s="1">
         <v>46149</v>
       </c>
@@ -6989,7 +6988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:24" hidden="1">
+    <row r="141" spans="1:24">
       <c r="A141" s="1">
         <v>46150</v>
       </c>
@@ -7042,7 +7041,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:24" hidden="1">
+    <row r="142" spans="1:24">
       <c r="A142" s="1">
         <v>46151</v>
       </c>
@@ -7095,7 +7094,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="143" spans="1:24" hidden="1">
+    <row r="143" spans="1:24">
       <c r="A143" s="1">
         <v>46152</v>
       </c>
@@ -7160,7 +7159,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="144" spans="1:24" hidden="1">
+    <row r="144" spans="1:24">
       <c r="A144" s="1">
         <v>46152</v>
       </c>
@@ -7207,7 +7206,7 @@
       <c r="T144" s="1"/>
       <c r="W144" s="1"/>
     </row>
-    <row r="145" spans="1:22" hidden="1">
+    <row r="145" spans="1:22">
       <c r="A145" s="1">
         <v>46153</v>
       </c>
@@ -7263,7 +7262,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="146" spans="1:22" hidden="1">
+    <row r="146" spans="1:22">
       <c r="A146" s="1">
         <v>46154</v>
       </c>
@@ -7303,7 +7302,12 @@
       <c r="Q146">
         <v>24</v>
       </c>
-      <c r="R146" s="1"/>
+      <c r="R146" s="1">
+        <v>46199</v>
+      </c>
+      <c r="S146" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="147" spans="1:22">
       <c r="A147" s="1">
@@ -7425,7 +7429,7 @@
       </c>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:22" hidden="1">
+    <row r="150" spans="1:22">
       <c r="A150" s="1">
         <v>46160</v>
       </c>
@@ -7472,7 +7476,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="151" spans="1:22" hidden="1">
+    <row r="151" spans="1:22">
       <c r="A151" s="1">
         <v>46161</v>
       </c>
@@ -7597,7 +7601,7 @@
       </c>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:22" hidden="1">
+    <row r="154" spans="1:22">
       <c r="A154" s="1">
         <v>46168</v>
       </c>
@@ -7642,7 +7646,7 @@
       </c>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:22" hidden="1">
+    <row r="155" spans="1:22">
       <c r="A155" s="1">
         <v>46170</v>
       </c>
@@ -8246,7 +8250,7 @@
       </c>
       <c r="R167" s="1"/>
     </row>
-    <row r="168" spans="1:18" hidden="1">
+    <row r="168" spans="1:18">
       <c r="A168" s="1">
         <v>46179</v>
       </c>
@@ -8291,7 +8295,7 @@
       </c>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18" hidden="1">
+    <row r="169" spans="1:18">
       <c r="A169" s="1">
         <v>46179</v>
       </c>
@@ -8603,7 +8607,7 @@
       </c>
       <c r="R175" s="1"/>
     </row>
-    <row r="176" spans="1:18" hidden="1">
+    <row r="176" spans="1:18">
       <c r="A176" s="1">
         <v>46186</v>
       </c>
@@ -8639,7 +8643,7 @@
       </c>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18" hidden="1">
+    <row r="177" spans="1:18">
       <c r="A177" s="1">
         <v>46187</v>
       </c>
@@ -8684,7 +8688,7 @@
       </c>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:18" hidden="1">
+    <row r="178" spans="1:18">
       <c r="A178" s="1">
         <v>46187</v>
       </c>
@@ -9078,35 +9082,276 @@
       <c r="R187" s="1"/>
     </row>
     <row r="188" spans="1:18">
-      <c r="A188" s="1"/>
+      <c r="A188" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B188">
+        <v>286</v>
+      </c>
+      <c r="C188">
+        <v>6800</v>
+      </c>
+      <c r="D188">
+        <v>6720</v>
+      </c>
+      <c r="E188">
+        <v>57</v>
+      </c>
+      <c r="F188" t="s">
+        <v>19</v>
+      </c>
+      <c r="G188">
+        <v>18</v>
+      </c>
+      <c r="I188">
+        <v>925</v>
+      </c>
+      <c r="K188">
+        <v>10</v>
+      </c>
+      <c r="L188">
+        <v>672</v>
+      </c>
       <c r="R188" s="1"/>
     </row>
     <row r="189" spans="1:18">
-      <c r="A189" s="1"/>
+      <c r="A189" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B189">
+        <v>287</v>
+      </c>
+      <c r="C189">
+        <v>6800</v>
+      </c>
+      <c r="D189">
+        <v>6720</v>
+      </c>
+      <c r="E189">
+        <v>57</v>
+      </c>
+      <c r="F189" t="s">
+        <v>19</v>
+      </c>
+      <c r="G189">
+        <v>20</v>
+      </c>
+      <c r="I189">
+        <v>925</v>
+      </c>
+      <c r="K189">
+        <v>10</v>
+      </c>
+      <c r="L189">
+        <v>672</v>
+      </c>
+      <c r="O189" s="1">
+        <v>46199</v>
+      </c>
+      <c r="P189" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q189">
+        <v>24</v>
+      </c>
       <c r="R189" s="1"/>
     </row>
     <row r="190" spans="1:18">
-      <c r="A190" s="1"/>
+      <c r="A190" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B190">
+        <v>288</v>
+      </c>
+      <c r="C190">
+        <v>6800</v>
+      </c>
+      <c r="D190">
+        <v>6720</v>
+      </c>
+      <c r="E190">
+        <v>57</v>
+      </c>
+      <c r="F190" t="s">
+        <v>19</v>
+      </c>
+      <c r="G190">
+        <v>62</v>
+      </c>
+      <c r="I190">
+        <v>925</v>
+      </c>
+      <c r="K190">
+        <v>10</v>
+      </c>
+      <c r="L190">
+        <v>672</v>
+      </c>
       <c r="R190" s="1"/>
     </row>
     <row r="191" spans="1:18">
-      <c r="A191" s="1"/>
+      <c r="A191" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B191">
+        <v>289</v>
+      </c>
+      <c r="C191">
+        <v>6800</v>
+      </c>
+      <c r="D191">
+        <v>6720</v>
+      </c>
+      <c r="E191">
+        <v>57</v>
+      </c>
+      <c r="F191" t="s">
+        <v>19</v>
+      </c>
+      <c r="G191">
+        <v>68</v>
+      </c>
+      <c r="I191">
+        <v>925</v>
+      </c>
+      <c r="K191">
+        <v>10</v>
+      </c>
+      <c r="L191">
+        <v>672</v>
+      </c>
       <c r="R191" s="1"/>
     </row>
     <row r="192" spans="1:18">
-      <c r="A192" s="1"/>
+      <c r="A192" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B192">
+        <v>290</v>
+      </c>
+      <c r="C192">
+        <v>6800</v>
+      </c>
+      <c r="D192">
+        <v>6720</v>
+      </c>
+      <c r="E192">
+        <v>57</v>
+      </c>
+      <c r="F192" t="s">
+        <v>19</v>
+      </c>
+      <c r="G192">
+        <v>39</v>
+      </c>
+      <c r="I192">
+        <v>925</v>
+      </c>
+      <c r="K192">
+        <v>10</v>
+      </c>
+      <c r="L192">
+        <v>672</v>
+      </c>
       <c r="R192" s="1"/>
     </row>
     <row r="193" spans="1:18">
-      <c r="A193" s="1"/>
+      <c r="A193" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B193">
+        <v>291</v>
+      </c>
+      <c r="C193">
+        <v>6800</v>
+      </c>
+      <c r="D193">
+        <v>6720</v>
+      </c>
+      <c r="E193">
+        <v>57</v>
+      </c>
+      <c r="F193" t="s">
+        <v>19</v>
+      </c>
+      <c r="G193">
+        <v>5</v>
+      </c>
+      <c r="I193">
+        <v>925</v>
+      </c>
+      <c r="K193">
+        <v>10</v>
+      </c>
+      <c r="L193">
+        <v>672</v>
+      </c>
       <c r="R193" s="1"/>
     </row>
     <row r="194" spans="1:18">
-      <c r="A194" s="1"/>
+      <c r="A194" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B194">
+        <v>292</v>
+      </c>
+      <c r="C194">
+        <v>6800</v>
+      </c>
+      <c r="D194">
+        <v>6720</v>
+      </c>
+      <c r="E194">
+        <v>57</v>
+      </c>
+      <c r="F194" t="s">
+        <v>19</v>
+      </c>
+      <c r="G194">
+        <v>49</v>
+      </c>
+      <c r="I194">
+        <v>925</v>
+      </c>
+      <c r="K194">
+        <v>10</v>
+      </c>
+      <c r="L194">
+        <v>672</v>
+      </c>
       <c r="R194" s="1"/>
     </row>
     <row r="195" spans="1:18">
-      <c r="A195" s="1"/>
+      <c r="A195" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B195">
+        <v>293</v>
+      </c>
+      <c r="C195">
+        <v>6800</v>
+      </c>
+      <c r="D195">
+        <v>6720</v>
+      </c>
+      <c r="E195">
+        <v>57</v>
+      </c>
+      <c r="F195" t="s">
+        <v>19</v>
+      </c>
+      <c r="G195">
+        <v>33</v>
+      </c>
+      <c r="I195">
+        <v>925</v>
+      </c>
+      <c r="K195">
+        <v>10</v>
+      </c>
+      <c r="L195">
+        <v>672</v>
+      </c>
       <c r="R195" s="1"/>
     </row>
     <row r="196" spans="1:18">
@@ -9256,12 +9501,8 @@
       <c r="A235" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X187">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="PURE GOLD"/>
-      </filters>
-    </filterColumn>
+  <autoFilter ref="A1:X195">
+    <filterColumn colId="5"/>
     <filterColumn colId="13"/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -7202,7 +7202,12 @@
       <c r="Q144">
         <v>23</v>
       </c>
-      <c r="R144" s="1"/>
+      <c r="R144" s="1">
+        <v>46200</v>
+      </c>
+      <c r="S144" t="s">
+        <v>27</v>
+      </c>
       <c r="T144" s="1"/>
       <c r="W144" s="1"/>
     </row>
@@ -7923,7 +7928,7 @@
       </c>
       <c r="R160" s="1"/>
     </row>
-    <row r="161" spans="1:18">
+    <row r="161" spans="1:19">
       <c r="A161" s="1">
         <v>46173</v>
       </c>
@@ -7971,7 +7976,7 @@
       </c>
       <c r="R161" s="1"/>
     </row>
-    <row r="162" spans="1:18">
+    <row r="162" spans="1:19">
       <c r="A162" s="1">
         <v>46175</v>
       </c>
@@ -8019,7 +8024,7 @@
       </c>
       <c r="R162" s="1"/>
     </row>
-    <row r="163" spans="1:18">
+    <row r="163" spans="1:19">
       <c r="A163" s="1">
         <v>46176</v>
       </c>
@@ -8064,7 +8069,7 @@
       </c>
       <c r="R163" s="1"/>
     </row>
-    <row r="164" spans="1:18">
+    <row r="164" spans="1:19">
       <c r="A164" s="1">
         <v>46176</v>
       </c>
@@ -8106,7 +8111,7 @@
       </c>
       <c r="R164" s="1"/>
     </row>
-    <row r="165" spans="1:18">
+    <row r="165" spans="1:19">
       <c r="A165" s="1">
         <v>46177</v>
       </c>
@@ -8154,7 +8159,7 @@
       </c>
       <c r="R165" s="1"/>
     </row>
-    <row r="166" spans="1:18">
+    <row r="166" spans="1:19">
       <c r="A166" s="1">
         <v>46178</v>
       </c>
@@ -8202,7 +8207,7 @@
       </c>
       <c r="R166" s="1"/>
     </row>
-    <row r="167" spans="1:18">
+    <row r="167" spans="1:19">
       <c r="A167" s="1">
         <v>46178</v>
       </c>
@@ -8250,7 +8255,7 @@
       </c>
       <c r="R167" s="1"/>
     </row>
-    <row r="168" spans="1:18">
+    <row r="168" spans="1:19">
       <c r="A168" s="1">
         <v>46179</v>
       </c>
@@ -8295,7 +8300,7 @@
       </c>
       <c r="R168" s="1"/>
     </row>
-    <row r="169" spans="1:18">
+    <row r="169" spans="1:19">
       <c r="A169" s="1">
         <v>46179</v>
       </c>
@@ -8341,9 +8346,14 @@
       <c r="Q169">
         <v>15</v>
       </c>
-      <c r="R169" s="1"/>
-    </row>
-    <row r="170" spans="1:18">
+      <c r="R169" s="1">
+        <v>46200</v>
+      </c>
+      <c r="S169" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19">
       <c r="A170" s="1">
         <v>46181</v>
       </c>
@@ -8391,7 +8401,7 @@
       </c>
       <c r="R170" s="1"/>
     </row>
-    <row r="171" spans="1:18">
+    <row r="171" spans="1:19">
       <c r="A171" s="1">
         <v>46182</v>
       </c>
@@ -8427,7 +8437,7 @@
       </c>
       <c r="R171" s="1"/>
     </row>
-    <row r="172" spans="1:18">
+    <row r="172" spans="1:19">
       <c r="A172" s="1">
         <v>46183</v>
       </c>
@@ -8472,7 +8482,7 @@
       </c>
       <c r="R172" s="1"/>
     </row>
-    <row r="173" spans="1:18">
+    <row r="173" spans="1:19">
       <c r="A173" s="1">
         <v>46184</v>
       </c>
@@ -8514,7 +8524,7 @@
       </c>
       <c r="R173" s="1"/>
     </row>
-    <row r="174" spans="1:18">
+    <row r="174" spans="1:19">
       <c r="A174" s="1">
         <v>46185</v>
       </c>
@@ -8562,7 +8572,7 @@
       </c>
       <c r="R174" s="1"/>
     </row>
-    <row r="175" spans="1:18">
+    <row r="175" spans="1:19">
       <c r="A175" s="1">
         <v>46185</v>
       </c>
@@ -8607,7 +8617,7 @@
       </c>
       <c r="R175" s="1"/>
     </row>
-    <row r="176" spans="1:18">
+    <row r="176" spans="1:19">
       <c r="A176" s="1">
         <v>46186</v>
       </c>
@@ -9112,6 +9122,15 @@
       <c r="L188">
         <v>672</v>
       </c>
+      <c r="O188" s="1">
+        <v>46200</v>
+      </c>
+      <c r="P188" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q188">
+        <v>23</v>
+      </c>
       <c r="R188" s="1"/>
     </row>
     <row r="189" spans="1:18">
@@ -9285,6 +9304,15 @@
       </c>
       <c r="L193">
         <v>672</v>
+      </c>
+      <c r="O193" s="1">
+        <v>46200</v>
+      </c>
+      <c r="P193" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q193">
+        <v>15</v>
       </c>
       <c r="R193" s="1"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -7211,7 +7211,7 @@
       <c r="T144" s="1"/>
       <c r="W144" s="1"/>
     </row>
-    <row r="145" spans="1:22">
+    <row r="145" spans="1:24">
       <c r="A145" s="1">
         <v>46153</v>
       </c>
@@ -7266,8 +7266,14 @@
       <c r="V145" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="146" spans="1:22">
+      <c r="W145" s="1">
+        <v>46201</v>
+      </c>
+      <c r="X145" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24">
       <c r="A146" s="1">
         <v>46154</v>
       </c>
@@ -7314,7 +7320,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="147" spans="1:22">
+    <row r="147" spans="1:24">
       <c r="A147" s="1">
         <v>46156</v>
       </c>
@@ -7356,7 +7362,7 @@
       </c>
       <c r="R147" s="1"/>
     </row>
-    <row r="148" spans="1:22">
+    <row r="148" spans="1:24">
       <c r="A148" s="1">
         <v>46156</v>
       </c>
@@ -7398,7 +7404,7 @@
       </c>
       <c r="R148" s="1"/>
     </row>
-    <row r="149" spans="1:22">
+    <row r="149" spans="1:24">
       <c r="A149" s="1">
         <v>46159</v>
       </c>
@@ -7434,7 +7440,7 @@
       </c>
       <c r="R149" s="1"/>
     </row>
-    <row r="150" spans="1:22">
+    <row r="150" spans="1:24">
       <c r="A150" s="1">
         <v>46160</v>
       </c>
@@ -7481,7 +7487,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="151" spans="1:22">
+    <row r="151" spans="1:24">
       <c r="A151" s="1">
         <v>46161</v>
       </c>
@@ -7528,7 +7534,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="152" spans="1:22">
+    <row r="152" spans="1:24">
       <c r="A152" s="1">
         <v>46165</v>
       </c>
@@ -7567,7 +7573,7 @@
       </c>
       <c r="R152" s="1"/>
     </row>
-    <row r="153" spans="1:22">
+    <row r="153" spans="1:24">
       <c r="A153" s="1">
         <v>46165</v>
       </c>
@@ -7606,7 +7612,7 @@
       </c>
       <c r="R153" s="1"/>
     </row>
-    <row r="154" spans="1:22">
+    <row r="154" spans="1:24">
       <c r="A154" s="1">
         <v>46168</v>
       </c>
@@ -7651,7 +7657,7 @@
       </c>
       <c r="R154" s="1"/>
     </row>
-    <row r="155" spans="1:22">
+    <row r="155" spans="1:24">
       <c r="A155" s="1">
         <v>46170</v>
       </c>
@@ -7696,7 +7702,7 @@
       </c>
       <c r="R155" s="1"/>
     </row>
-    <row r="156" spans="1:22">
+    <row r="156" spans="1:24">
       <c r="A156" s="1">
         <v>46170</v>
       </c>
@@ -7746,7 +7752,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="157" spans="1:22">
+    <row r="157" spans="1:24">
       <c r="A157" s="1">
         <v>46170</v>
       </c>
@@ -7796,7 +7802,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:22">
+    <row r="158" spans="1:24">
       <c r="A158" s="1">
         <v>46171</v>
       </c>
@@ -7832,7 +7838,7 @@
       </c>
       <c r="R158" s="1"/>
     </row>
-    <row r="159" spans="1:22">
+    <row r="159" spans="1:24">
       <c r="A159" s="1">
         <v>46172</v>
       </c>
@@ -7880,7 +7886,7 @@
       </c>
       <c r="R159" s="1"/>
     </row>
-    <row r="160" spans="1:22">
+    <row r="160" spans="1:24">
       <c r="A160" s="1">
         <v>46111</v>
       </c>
@@ -9088,6 +9094,15 @@
       </c>
       <c r="L187">
         <v>672</v>
+      </c>
+      <c r="O187" s="1">
+        <v>46201</v>
+      </c>
+      <c r="P187" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q187">
+        <v>13</v>
       </c>
       <c r="R187" s="1"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -193,7 +193,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,13 +208,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -226,10 +238,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -248,8 +261,13 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -643,8 +661,8 @@
       <c r="B2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="2">
-        <v>3755</v>
+      <c r="C2" s="11">
+        <v>3000</v>
       </c>
       <c r="D2" s="2">
         <v>12024</v>
@@ -3680,8 +3698,8 @@
       <c r="B70">
         <v>4125</v>
       </c>
-      <c r="C70">
-        <v>8000</v>
+      <c r="C70" s="10">
+        <v>7500</v>
       </c>
       <c r="D70">
         <v>7200</v>
@@ -5259,8 +5277,8 @@
       <c r="B103">
         <v>208</v>
       </c>
-      <c r="C103">
-        <v>1500</v>
+      <c r="C103" s="10">
+        <v>50</v>
       </c>
       <c r="D103">
         <v>5624</v>
@@ -7166,8 +7184,8 @@
       <c r="B144" t="s">
         <v>54</v>
       </c>
-      <c r="C144">
-        <v>6500</v>
+      <c r="C144" s="10">
+        <v>5000</v>
       </c>
       <c r="D144">
         <v>5624</v>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -9239,6 +9239,9 @@
       <c r="L190">
         <v>672</v>
       </c>
+      <c r="N190" t="s">
+        <v>43</v>
+      </c>
       <c r="R190" s="1"/>
     </row>
     <row r="191" spans="1:18">
@@ -9271,6 +9274,9 @@
       </c>
       <c r="L191">
         <v>672</v>
+      </c>
+      <c r="N191" t="s">
+        <v>43</v>
       </c>
       <c r="R191" s="1"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="56">
   <si>
     <t>ENDS</t>
   </si>
@@ -7673,7 +7673,12 @@
       <c r="Q154">
         <v>28</v>
       </c>
-      <c r="R154" s="1"/>
+      <c r="R154" s="1">
+        <v>46200</v>
+      </c>
+      <c r="S154" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="155" spans="1:24">
       <c r="A155" s="1">
@@ -8741,6 +8746,9 @@
       <c r="F178" t="s">
         <v>4</v>
       </c>
+      <c r="H178">
+        <v>11</v>
+      </c>
       <c r="I178">
         <v>1050</v>
       </c>
@@ -8777,6 +8785,9 @@
       <c r="G179">
         <v>21</v>
       </c>
+      <c r="H179">
+        <v>2</v>
+      </c>
       <c r="I179">
         <v>925</v>
       </c>
@@ -8822,6 +8833,9 @@
       <c r="G180">
         <v>40</v>
       </c>
+      <c r="H180">
+        <v>21</v>
+      </c>
       <c r="I180">
         <v>925</v>
       </c>
@@ -8861,6 +8875,9 @@
       <c r="G181">
         <v>31</v>
       </c>
+      <c r="H181">
+        <v>22</v>
+      </c>
       <c r="I181">
         <v>925</v>
       </c>
@@ -8903,6 +8920,9 @@
       <c r="G182">
         <v>45</v>
       </c>
+      <c r="H182">
+        <v>18</v>
+      </c>
       <c r="I182">
         <v>925</v>
       </c>
@@ -8945,6 +8965,9 @@
       <c r="G183">
         <v>50</v>
       </c>
+      <c r="H183">
+        <v>4</v>
+      </c>
       <c r="I183">
         <v>925</v>
       </c>
@@ -8978,6 +9001,9 @@
       <c r="G184">
         <v>29</v>
       </c>
+      <c r="H184">
+        <v>7</v>
+      </c>
       <c r="I184">
         <v>925</v>
       </c>
@@ -9062,6 +9088,9 @@
       <c r="G186">
         <v>25</v>
       </c>
+      <c r="H186">
+        <v>2</v>
+      </c>
       <c r="I186">
         <v>925</v>
       </c>
@@ -9104,6 +9133,9 @@
       <c r="G187">
         <v>11</v>
       </c>
+      <c r="H187">
+        <v>25</v>
+      </c>
       <c r="I187">
         <v>925</v>
       </c>
@@ -9146,6 +9178,9 @@
       <c r="G188">
         <v>18</v>
       </c>
+      <c r="H188">
+        <v>11</v>
+      </c>
       <c r="I188">
         <v>925</v>
       </c>
@@ -9188,6 +9223,9 @@
       <c r="G189">
         <v>20</v>
       </c>
+      <c r="H189">
+        <v>18</v>
+      </c>
       <c r="I189">
         <v>925</v>
       </c>
@@ -9230,6 +9268,9 @@
       <c r="G190">
         <v>62</v>
       </c>
+      <c r="H190">
+        <v>13</v>
+      </c>
       <c r="I190">
         <v>925</v>
       </c>
@@ -9266,6 +9307,9 @@
       <c r="G191">
         <v>68</v>
       </c>
+      <c r="H191">
+        <v>17</v>
+      </c>
       <c r="I191">
         <v>925</v>
       </c>
@@ -9302,6 +9346,9 @@
       <c r="G192">
         <v>39</v>
       </c>
+      <c r="H192">
+        <v>13</v>
+      </c>
       <c r="I192">
         <v>925</v>
       </c>
@@ -9310,6 +9357,15 @@
       </c>
       <c r="L192">
         <v>672</v>
+      </c>
+      <c r="O192" s="1">
+        <v>46201</v>
+      </c>
+      <c r="P192" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q192">
+        <v>28</v>
       </c>
       <c r="R192" s="1"/>
     </row>
@@ -9335,6 +9391,9 @@
       <c r="G193">
         <v>5</v>
       </c>
+      <c r="H193">
+        <v>12</v>
+      </c>
       <c r="I193">
         <v>925</v>
       </c>
@@ -9377,6 +9436,9 @@
       <c r="G194">
         <v>49</v>
       </c>
+      <c r="H194">
+        <v>13</v>
+      </c>
       <c r="I194">
         <v>925</v>
       </c>
@@ -9410,6 +9472,9 @@
       <c r="G195">
         <v>33</v>
       </c>
+      <c r="H195">
+        <v>15</v>
+      </c>
       <c r="I195">
         <v>925</v>
       </c>
@@ -9422,11 +9487,72 @@
       <c r="R195" s="1"/>
     </row>
     <row r="196" spans="1:18">
-      <c r="A196" s="1"/>
+      <c r="A196" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B196">
+        <v>294</v>
+      </c>
+      <c r="C196">
+        <v>6800</v>
+      </c>
+      <c r="D196">
+        <v>6720</v>
+      </c>
+      <c r="E196">
+        <v>57</v>
+      </c>
+      <c r="F196" t="s">
+        <v>19</v>
+      </c>
+      <c r="G196">
+        <v>35</v>
+      </c>
+      <c r="H196">
+        <v>7</v>
+      </c>
+      <c r="I196">
+        <v>925</v>
+      </c>
+      <c r="K196">
+        <v>10</v>
+      </c>
+      <c r="L196">
+        <v>672</v>
+      </c>
       <c r="R196" s="1"/>
     </row>
     <row r="197" spans="1:18">
-      <c r="A197" s="1"/>
+      <c r="A197" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B197">
+        <v>295</v>
+      </c>
+      <c r="C197">
+        <v>6800</v>
+      </c>
+      <c r="D197">
+        <v>6720</v>
+      </c>
+      <c r="E197">
+        <v>57</v>
+      </c>
+      <c r="F197" t="s">
+        <v>19</v>
+      </c>
+      <c r="H197">
+        <v>21</v>
+      </c>
+      <c r="I197">
+        <v>925</v>
+      </c>
+      <c r="K197">
+        <v>10</v>
+      </c>
+      <c r="L197">
+        <v>672</v>
+      </c>
       <c r="R197" s="1"/>
     </row>
     <row r="198" spans="1:18">

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$197</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="57">
   <si>
     <t>ENDS</t>
   </si>
@@ -187,6 +187,9 @@
   </si>
   <si>
     <t>SUMIT</t>
+  </si>
+  <si>
+    <t>CHOTA</t>
   </si>
 </sst>
 </file>
@@ -7723,7 +7726,12 @@
       <c r="Q155">
         <v>26</v>
       </c>
-      <c r="R155" s="1"/>
+      <c r="R155" s="1">
+        <v>46202</v>
+      </c>
+      <c r="S155" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="156" spans="1:24">
       <c r="A156" s="1">
@@ -8327,7 +8335,12 @@
       <c r="Q168">
         <v>16</v>
       </c>
-      <c r="R168" s="1"/>
+      <c r="R168" s="1">
+        <v>46202</v>
+      </c>
+      <c r="S168" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="169" spans="1:19">
       <c r="A169" s="1">
@@ -8680,6 +8693,9 @@
       <c r="M176" t="s">
         <v>55</v>
       </c>
+      <c r="N176" t="s">
+        <v>42</v>
+      </c>
       <c r="R176" s="1"/>
     </row>
     <row r="177" spans="1:18">
@@ -8746,6 +8762,9 @@
       <c r="F178" t="s">
         <v>4</v>
       </c>
+      <c r="G178">
+        <v>10</v>
+      </c>
       <c r="H178">
         <v>11</v>
       </c>
@@ -8760,6 +8779,9 @@
       </c>
       <c r="M178" t="s">
         <v>45</v>
+      </c>
+      <c r="N178" t="s">
+        <v>42</v>
       </c>
       <c r="R178" s="1"/>
     </row>
@@ -8887,6 +8909,9 @@
       <c r="L181">
         <v>672</v>
       </c>
+      <c r="M181" t="s">
+        <v>56</v>
+      </c>
       <c r="O181" s="1">
         <v>46193</v>
       </c>
@@ -8932,6 +8957,9 @@
       <c r="L182">
         <v>672</v>
       </c>
+      <c r="M182" t="s">
+        <v>45</v>
+      </c>
       <c r="O182" s="1">
         <v>46193</v>
       </c>
@@ -8977,6 +9005,9 @@
       <c r="L183">
         <v>672</v>
       </c>
+      <c r="M183" t="s">
+        <v>45</v>
+      </c>
       <c r="R183" s="1"/>
     </row>
     <row r="184" spans="1:18">
@@ -9013,6 +9044,9 @@
       <c r="L184">
         <v>672</v>
       </c>
+      <c r="M184" t="s">
+        <v>45</v>
+      </c>
       <c r="O184" s="1">
         <v>46195</v>
       </c>
@@ -9055,6 +9089,9 @@
       <c r="L185">
         <v>672</v>
       </c>
+      <c r="M185" t="s">
+        <v>45</v>
+      </c>
       <c r="O185" s="1">
         <v>46195</v>
       </c>
@@ -9100,6 +9137,9 @@
       <c r="L186">
         <v>672</v>
       </c>
+      <c r="M186" t="s">
+        <v>45</v>
+      </c>
       <c r="O186" s="1">
         <v>46197</v>
       </c>
@@ -9145,6 +9185,9 @@
       <c r="L187">
         <v>672</v>
       </c>
+      <c r="M187" t="s">
+        <v>45</v>
+      </c>
       <c r="O187" s="1">
         <v>46201</v>
       </c>
@@ -9190,6 +9233,9 @@
       <c r="L188">
         <v>672</v>
       </c>
+      <c r="M188" t="s">
+        <v>45</v>
+      </c>
       <c r="O188" s="1">
         <v>46200</v>
       </c>
@@ -9235,6 +9281,9 @@
       <c r="L189">
         <v>672</v>
       </c>
+      <c r="M189" t="s">
+        <v>45</v>
+      </c>
       <c r="O189" s="1">
         <v>46199</v>
       </c>
@@ -9280,6 +9329,9 @@
       <c r="L190">
         <v>672</v>
       </c>
+      <c r="M190" t="s">
+        <v>45</v>
+      </c>
       <c r="N190" t="s">
         <v>43</v>
       </c>
@@ -9319,6 +9371,9 @@
       <c r="L191">
         <v>672</v>
       </c>
+      <c r="M191" t="s">
+        <v>45</v>
+      </c>
       <c r="N191" t="s">
         <v>43</v>
       </c>
@@ -9358,6 +9413,9 @@
       <c r="L192">
         <v>672</v>
       </c>
+      <c r="M192" t="s">
+        <v>45</v>
+      </c>
       <c r="O192" s="1">
         <v>46201</v>
       </c>
@@ -9403,6 +9461,9 @@
       <c r="L193">
         <v>672</v>
       </c>
+      <c r="M193" t="s">
+        <v>45</v>
+      </c>
       <c r="O193" s="1">
         <v>46200</v>
       </c>
@@ -9448,6 +9509,9 @@
       <c r="L194">
         <v>672</v>
       </c>
+      <c r="M194" t="s">
+        <v>45</v>
+      </c>
       <c r="R194" s="1"/>
     </row>
     <row r="195" spans="1:18">
@@ -9484,6 +9548,18 @@
       <c r="L195">
         <v>672</v>
       </c>
+      <c r="M195" t="s">
+        <v>45</v>
+      </c>
+      <c r="O195" s="1">
+        <v>46203</v>
+      </c>
+      <c r="P195" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q195">
+        <v>16</v>
+      </c>
       <c r="R195" s="1"/>
     </row>
     <row r="196" spans="1:18">
@@ -9520,6 +9596,9 @@
       <c r="L196">
         <v>672</v>
       </c>
+      <c r="M196" t="s">
+        <v>45</v>
+      </c>
       <c r="R196" s="1"/>
     </row>
     <row r="197" spans="1:18">
@@ -9541,6 +9620,9 @@
       <c r="F197" t="s">
         <v>19</v>
       </c>
+      <c r="G197">
+        <v>26</v>
+      </c>
       <c r="H197">
         <v>21</v>
       </c>
@@ -9553,22 +9635,168 @@
       <c r="L197">
         <v>672</v>
       </c>
+      <c r="M197" t="s">
+        <v>45</v>
+      </c>
+      <c r="O197" s="1">
+        <v>46203</v>
+      </c>
+      <c r="P197" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q197">
+        <v>26</v>
+      </c>
       <c r="R197" s="1"/>
     </row>
     <row r="198" spans="1:18">
-      <c r="A198" s="1"/>
+      <c r="A198" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B198">
+        <v>296</v>
+      </c>
+      <c r="C198">
+        <v>6800</v>
+      </c>
+      <c r="D198">
+        <v>6720</v>
+      </c>
+      <c r="E198">
+        <v>57</v>
+      </c>
+      <c r="F198" t="s">
+        <v>19</v>
+      </c>
+      <c r="G198">
+        <v>74</v>
+      </c>
+      <c r="H198">
+        <v>7</v>
+      </c>
+      <c r="I198">
+        <v>925</v>
+      </c>
+      <c r="K198">
+        <v>10</v>
+      </c>
+      <c r="L198">
+        <v>672</v>
+      </c>
+      <c r="M198" t="s">
+        <v>44</v>
+      </c>
       <c r="R198" s="1"/>
     </row>
     <row r="199" spans="1:18">
-      <c r="A199" s="1"/>
+      <c r="A199" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B199">
+        <v>297</v>
+      </c>
+      <c r="C199">
+        <v>6800</v>
+      </c>
+      <c r="D199">
+        <v>6720</v>
+      </c>
+      <c r="E199">
+        <v>57</v>
+      </c>
+      <c r="F199" t="s">
+        <v>19</v>
+      </c>
+      <c r="G199">
+        <v>41</v>
+      </c>
+      <c r="H199">
+        <v>18</v>
+      </c>
+      <c r="I199">
+        <v>925</v>
+      </c>
+      <c r="K199">
+        <v>10</v>
+      </c>
+      <c r="L199">
+        <v>672</v>
+      </c>
+      <c r="M199" t="s">
+        <v>45</v>
+      </c>
       <c r="R199" s="1"/>
     </row>
     <row r="200" spans="1:18">
-      <c r="A200" s="1"/>
+      <c r="A200" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B200">
+        <v>298</v>
+      </c>
+      <c r="C200">
+        <v>680</v>
+      </c>
+      <c r="D200">
+        <v>6720</v>
+      </c>
+      <c r="E200">
+        <v>57</v>
+      </c>
+      <c r="F200" t="s">
+        <v>19</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>925</v>
+      </c>
+      <c r="K200">
+        <v>10</v>
+      </c>
+      <c r="L200">
+        <v>672</v>
+      </c>
+      <c r="M200" t="s">
+        <v>45</v>
+      </c>
       <c r="R200" s="1"/>
     </row>
     <row r="201" spans="1:18">
-      <c r="A201" s="1"/>
+      <c r="A201" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B201">
+        <v>299</v>
+      </c>
+      <c r="C201">
+        <v>6800</v>
+      </c>
+      <c r="D201">
+        <v>6720</v>
+      </c>
+      <c r="E201">
+        <v>57</v>
+      </c>
+      <c r="F201" t="s">
+        <v>19</v>
+      </c>
+      <c r="H201">
+        <v>7</v>
+      </c>
+      <c r="I201">
+        <v>925</v>
+      </c>
+      <c r="K201">
+        <v>10</v>
+      </c>
+      <c r="L201">
+        <v>672</v>
+      </c>
+      <c r="M201" t="s">
+        <v>45</v>
+      </c>
       <c r="R201" s="1"/>
     </row>
     <row r="202" spans="1:18">
@@ -9694,7 +9922,7 @@
       <c r="A235" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X195">
+  <autoFilter ref="A1:X197">
     <filterColumn colId="5"/>
     <filterColumn colId="13"/>
   </autoFilter>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$201</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="57">
   <si>
     <t>ENDS</t>
   </si>
@@ -563,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X235"/>
+  <dimension ref="A1:AA235"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -581,6 +581,7 @@
     <col min="22" max="22" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10.85546875" customWidth="1"/>
     <col min="24" max="24" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" s="2" customFormat="1" ht="42.75" customHeight="1">
@@ -8698,7 +8699,7 @@
       </c>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:18">
+    <row r="177" spans="1:27">
       <c r="A177" s="1">
         <v>46187</v>
       </c>
@@ -8743,7 +8744,7 @@
       </c>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:18">
+    <row r="178" spans="1:27">
       <c r="A178" s="1">
         <v>46187</v>
       </c>
@@ -8785,7 +8786,7 @@
       </c>
       <c r="R178" s="1"/>
     </row>
-    <row r="179" spans="1:18">
+    <row r="179" spans="1:27">
       <c r="A179" s="1">
         <v>46188</v>
       </c>
@@ -8833,7 +8834,7 @@
       </c>
       <c r="R179" s="1"/>
     </row>
-    <row r="180" spans="1:18">
+    <row r="180" spans="1:27">
       <c r="A180" s="1">
         <v>46189</v>
       </c>
@@ -8875,7 +8876,7 @@
       </c>
       <c r="R180" s="1"/>
     </row>
-    <row r="181" spans="1:18">
+    <row r="181" spans="1:27">
       <c r="A181" s="1">
         <v>46190</v>
       </c>
@@ -8923,7 +8924,7 @@
       </c>
       <c r="R181" s="1"/>
     </row>
-    <row r="182" spans="1:18">
+    <row r="182" spans="1:27">
       <c r="A182" s="1">
         <v>46191</v>
       </c>
@@ -8960,18 +8961,21 @@
       <c r="M182" t="s">
         <v>45</v>
       </c>
-      <c r="O182" s="1">
+      <c r="N182" t="s">
+        <v>43</v>
+      </c>
+      <c r="R182" s="1"/>
+      <c r="Y182" s="1">
         <v>46193</v>
       </c>
-      <c r="P182" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q182">
+      <c r="Z182" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA182">
         <v>6</v>
       </c>
-      <c r="R182" s="1"/>
-    </row>
-    <row r="183" spans="1:18">
+    </row>
+    <row r="183" spans="1:27">
       <c r="A183" s="1">
         <v>46191</v>
       </c>
@@ -9008,9 +9012,12 @@
       <c r="M183" t="s">
         <v>45</v>
       </c>
+      <c r="N183" t="s">
+        <v>43</v>
+      </c>
       <c r="R183" s="1"/>
     </row>
-    <row r="184" spans="1:18">
+    <row r="184" spans="1:27">
       <c r="A184" s="1">
         <v>46192</v>
       </c>
@@ -9058,7 +9065,7 @@
       </c>
       <c r="R184" s="1"/>
     </row>
-    <row r="185" spans="1:18">
+    <row r="185" spans="1:27">
       <c r="A185" s="1">
         <v>46193</v>
       </c>
@@ -9103,7 +9110,7 @@
       </c>
       <c r="R185" s="1"/>
     </row>
-    <row r="186" spans="1:18">
+    <row r="186" spans="1:27">
       <c r="A186" s="1">
         <v>46193</v>
       </c>
@@ -9151,7 +9158,7 @@
       </c>
       <c r="R186" s="1"/>
     </row>
-    <row r="187" spans="1:18">
+    <row r="187" spans="1:27">
       <c r="A187" s="1">
         <v>46194</v>
       </c>
@@ -9199,7 +9206,7 @@
       </c>
       <c r="R187" s="1"/>
     </row>
-    <row r="188" spans="1:18">
+    <row r="188" spans="1:27">
       <c r="A188" s="1">
         <v>46195</v>
       </c>
@@ -9247,7 +9254,7 @@
       </c>
       <c r="R188" s="1"/>
     </row>
-    <row r="189" spans="1:18">
+    <row r="189" spans="1:27">
       <c r="A189" s="1">
         <v>46195</v>
       </c>
@@ -9295,7 +9302,7 @@
       </c>
       <c r="R189" s="1"/>
     </row>
-    <row r="190" spans="1:18">
+    <row r="190" spans="1:27">
       <c r="A190" s="1">
         <v>46196</v>
       </c>
@@ -9337,7 +9344,7 @@
       </c>
       <c r="R190" s="1"/>
     </row>
-    <row r="191" spans="1:18">
+    <row r="191" spans="1:27">
       <c r="A191" s="1">
         <v>46196</v>
       </c>
@@ -9379,7 +9386,7 @@
       </c>
       <c r="R191" s="1"/>
     </row>
-    <row r="192" spans="1:18">
+    <row r="192" spans="1:27">
       <c r="A192" s="1">
         <v>46197</v>
       </c>
@@ -9686,6 +9693,9 @@
       <c r="M198" t="s">
         <v>44</v>
       </c>
+      <c r="N198" t="s">
+        <v>43</v>
+      </c>
       <c r="R198" s="1"/>
     </row>
     <row r="199" spans="1:18">
@@ -9725,6 +9735,9 @@
       <c r="M199" t="s">
         <v>45</v>
       </c>
+      <c r="N199" t="s">
+        <v>43</v>
+      </c>
       <c r="R199" s="1"/>
     </row>
     <row r="200" spans="1:18">
@@ -9922,7 +9935,7 @@
       <c r="A235" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X197">
+  <autoFilter ref="A1:X201">
     <filterColumn colId="5"/>
     <filterColumn colId="13"/>
   </autoFilter>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -12,14 +12,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$X$203</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="59">
   <si>
     <t>ENDS</t>
   </si>
@@ -190,6 +190,12 @@
   </si>
   <si>
     <t>CHOTA</t>
+  </si>
+  <si>
+    <t>277A</t>
+  </si>
+  <si>
+    <t>296A</t>
   </si>
 </sst>
 </file>
@@ -563,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA235"/>
+  <dimension ref="A1:Y237"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -8699,7 +8705,7 @@
       </c>
       <c r="R176" s="1"/>
     </row>
-    <row r="177" spans="1:27">
+    <row r="177" spans="1:25">
       <c r="A177" s="1">
         <v>46187</v>
       </c>
@@ -8744,7 +8750,7 @@
       </c>
       <c r="R177" s="1"/>
     </row>
-    <row r="178" spans="1:27">
+    <row r="178" spans="1:25">
       <c r="A178" s="1">
         <v>46187</v>
       </c>
@@ -8786,7 +8792,7 @@
       </c>
       <c r="R178" s="1"/>
     </row>
-    <row r="179" spans="1:27">
+    <row r="179" spans="1:25">
       <c r="A179" s="1">
         <v>46188</v>
       </c>
@@ -8806,7 +8812,7 @@
         <v>19</v>
       </c>
       <c r="G179">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H179">
         <v>2</v>
@@ -8834,7 +8840,7 @@
       </c>
       <c r="R179" s="1"/>
     </row>
-    <row r="180" spans="1:27">
+    <row r="180" spans="1:25">
       <c r="A180" s="1">
         <v>46189</v>
       </c>
@@ -8876,7 +8882,7 @@
       </c>
       <c r="R180" s="1"/>
     </row>
-    <row r="181" spans="1:27">
+    <row r="181" spans="1:25">
       <c r="A181" s="1">
         <v>46190</v>
       </c>
@@ -8924,7 +8930,7 @@
       </c>
       <c r="R181" s="1"/>
     </row>
-    <row r="182" spans="1:27">
+    <row r="182" spans="1:25">
       <c r="A182" s="1">
         <v>46191</v>
       </c>
@@ -8965,17 +8971,9 @@
         <v>43</v>
       </c>
       <c r="R182" s="1"/>
-      <c r="Y182" s="1">
-        <v>46193</v>
-      </c>
-      <c r="Z182" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA182">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="183" spans="1:27">
+      <c r="Y182" s="1"/>
+    </row>
+    <row r="183" spans="1:25">
       <c r="A183" s="1">
         <v>46191</v>
       </c>
@@ -9017,7 +9015,7 @@
       </c>
       <c r="R183" s="1"/>
     </row>
-    <row r="184" spans="1:27">
+    <row r="184" spans="1:25">
       <c r="A184" s="1">
         <v>46192</v>
       </c>
@@ -9065,7 +9063,7 @@
       </c>
       <c r="R184" s="1"/>
     </row>
-    <row r="185" spans="1:27">
+    <row r="185" spans="1:25">
       <c r="A185" s="1">
         <v>46193</v>
       </c>
@@ -9110,7 +9108,7 @@
       </c>
       <c r="R185" s="1"/>
     </row>
-    <row r="186" spans="1:27">
+    <row r="186" spans="1:25">
       <c r="A186" s="1">
         <v>46193</v>
       </c>
@@ -9158,7 +9156,7 @@
       </c>
       <c r="R186" s="1"/>
     </row>
-    <row r="187" spans="1:27">
+    <row r="187" spans="1:25">
       <c r="A187" s="1">
         <v>46194</v>
       </c>
@@ -9206,7 +9204,7 @@
       </c>
       <c r="R187" s="1"/>
     </row>
-    <row r="188" spans="1:27">
+    <row r="188" spans="1:25">
       <c r="A188" s="1">
         <v>46195</v>
       </c>
@@ -9254,7 +9252,7 @@
       </c>
       <c r="R188" s="1"/>
     </row>
-    <row r="189" spans="1:27">
+    <row r="189" spans="1:25">
       <c r="A189" s="1">
         <v>46195</v>
       </c>
@@ -9302,7 +9300,7 @@
       </c>
       <c r="R189" s="1"/>
     </row>
-    <row r="190" spans="1:27">
+    <row r="190" spans="1:25">
       <c r="A190" s="1">
         <v>46196</v>
       </c>
@@ -9344,7 +9342,7 @@
       </c>
       <c r="R190" s="1"/>
     </row>
-    <row r="191" spans="1:27">
+    <row r="191" spans="1:25">
       <c r="A191" s="1">
         <v>46196</v>
       </c>
@@ -9386,7 +9384,7 @@
       </c>
       <c r="R191" s="1"/>
     </row>
-    <row r="192" spans="1:27">
+    <row r="192" spans="1:25">
       <c r="A192" s="1">
         <v>46197</v>
       </c>
@@ -9742,13 +9740,13 @@
     </row>
     <row r="200" spans="1:18">
       <c r="A200" s="1">
-        <v>46204</v>
-      </c>
-      <c r="B200">
-        <v>298</v>
+        <v>46188</v>
+      </c>
+      <c r="B200" t="s">
+        <v>57</v>
       </c>
       <c r="C200">
-        <v>680</v>
+        <v>6800</v>
       </c>
       <c r="D200">
         <v>6720</v>
@@ -9759,8 +9757,8 @@
       <c r="F200" t="s">
         <v>19</v>
       </c>
-      <c r="H200">
-        <v>0</v>
+      <c r="G200">
+        <v>21</v>
       </c>
       <c r="I200">
         <v>925</v>
@@ -9774,14 +9772,23 @@
       <c r="M200" t="s">
         <v>45</v>
       </c>
+      <c r="O200" s="1">
+        <v>46193</v>
+      </c>
+      <c r="P200" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q200">
+        <v>6</v>
+      </c>
       <c r="R200" s="1"/>
     </row>
     <row r="201" spans="1:18">
       <c r="A201" s="1">
-        <v>46205</v>
-      </c>
-      <c r="B201">
-        <v>299</v>
+        <v>46201</v>
+      </c>
+      <c r="B201" t="s">
+        <v>58</v>
       </c>
       <c r="C201">
         <v>6800</v>
@@ -9795,8 +9802,8 @@
       <c r="F201" t="s">
         <v>19</v>
       </c>
-      <c r="H201">
-        <v>7</v>
+      <c r="G201">
+        <v>27</v>
       </c>
       <c r="I201">
         <v>925</v>
@@ -9813,11 +9820,75 @@
       <c r="R201" s="1"/>
     </row>
     <row r="202" spans="1:18">
-      <c r="A202" s="1"/>
+      <c r="A202" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B202">
+        <v>298</v>
+      </c>
+      <c r="C202">
+        <v>6800</v>
+      </c>
+      <c r="D202">
+        <v>6720</v>
+      </c>
+      <c r="E202">
+        <v>57</v>
+      </c>
+      <c r="F202" t="s">
+        <v>19</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <v>925</v>
+      </c>
+      <c r="K202">
+        <v>10</v>
+      </c>
+      <c r="L202">
+        <v>672</v>
+      </c>
+      <c r="M202" t="s">
+        <v>45</v>
+      </c>
       <c r="R202" s="1"/>
     </row>
     <row r="203" spans="1:18">
-      <c r="A203" s="1"/>
+      <c r="A203" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B203">
+        <v>299</v>
+      </c>
+      <c r="C203">
+        <v>6800</v>
+      </c>
+      <c r="D203">
+        <v>6720</v>
+      </c>
+      <c r="E203">
+        <v>57</v>
+      </c>
+      <c r="F203" t="s">
+        <v>19</v>
+      </c>
+      <c r="H203">
+        <v>7</v>
+      </c>
+      <c r="I203">
+        <v>925</v>
+      </c>
+      <c r="K203">
+        <v>10</v>
+      </c>
+      <c r="L203">
+        <v>672</v>
+      </c>
+      <c r="M203" t="s">
+        <v>45</v>
+      </c>
       <c r="R203" s="1"/>
     </row>
     <row r="204" spans="1:18">
@@ -9894,9 +9965,11 @@
     </row>
     <row r="222" spans="1:18">
       <c r="A222" s="1"/>
+      <c r="R222" s="1"/>
     </row>
     <row r="223" spans="1:18">
       <c r="A223" s="1"/>
+      <c r="R223" s="1"/>
     </row>
     <row r="224" spans="1:18">
       <c r="A224" s="1"/>
@@ -9934,8 +10007,14 @@
     <row r="235" spans="1:1">
       <c r="A235" s="1"/>
     </row>
+    <row r="236" spans="1:1">
+      <c r="A236" s="1"/>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237" s="1"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X201">
+  <autoFilter ref="A1:X203">
     <filterColumn colId="5"/>
     <filterColumn colId="13"/>
   </autoFilter>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="59">
   <si>
     <t>ENDS</t>
   </si>
@@ -7430,7 +7430,12 @@
       <c r="Q148">
         <v>21</v>
       </c>
-      <c r="R148" s="1"/>
+      <c r="R148" s="1">
+        <v>46207</v>
+      </c>
+      <c r="S148" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="149" spans="1:24">
       <c r="A149" s="1">
@@ -9517,6 +9522,15 @@
       <c r="M194" t="s">
         <v>45</v>
       </c>
+      <c r="O194" s="1">
+        <v>46207</v>
+      </c>
+      <c r="P194" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q194">
+        <v>21</v>
+      </c>
       <c r="R194" s="1"/>
     </row>
     <row r="195" spans="1:18">
@@ -9838,6 +9852,9 @@
       <c r="F202" t="s">
         <v>19</v>
       </c>
+      <c r="G202">
+        <v>37</v>
+      </c>
       <c r="H202">
         <v>0</v>
       </c>
@@ -9892,31 +9909,267 @@
       <c r="R203" s="1"/>
     </row>
     <row r="204" spans="1:18">
-      <c r="A204" s="1"/>
+      <c r="A204" s="1">
+        <v>46205</v>
+      </c>
+      <c r="B204">
+        <v>300</v>
+      </c>
+      <c r="C204">
+        <v>6800</v>
+      </c>
+      <c r="D204">
+        <v>6720</v>
+      </c>
+      <c r="E204">
+        <v>57</v>
+      </c>
+      <c r="F204" t="s">
+        <v>19</v>
+      </c>
+      <c r="G204">
+        <v>50</v>
+      </c>
+      <c r="H204">
+        <v>10</v>
+      </c>
+      <c r="I204">
+        <v>925</v>
+      </c>
+      <c r="K204">
+        <v>10</v>
+      </c>
+      <c r="L204">
+        <v>672</v>
+      </c>
+      <c r="M204" t="s">
+        <v>45</v>
+      </c>
       <c r="R204" s="1"/>
     </row>
     <row r="205" spans="1:18">
-      <c r="A205" s="1"/>
+      <c r="A205" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B205">
+        <v>301</v>
+      </c>
+      <c r="C205">
+        <v>6000</v>
+      </c>
+      <c r="D205">
+        <v>6720</v>
+      </c>
+      <c r="E205">
+        <v>57</v>
+      </c>
+      <c r="F205" t="s">
+        <v>19</v>
+      </c>
+      <c r="G205">
+        <v>3</v>
+      </c>
+      <c r="I205">
+        <v>925</v>
+      </c>
+      <c r="K205">
+        <v>10</v>
+      </c>
+      <c r="L205">
+        <v>672</v>
+      </c>
+      <c r="M205" t="s">
+        <v>45</v>
+      </c>
       <c r="R205" s="1"/>
     </row>
     <row r="206" spans="1:18">
-      <c r="A206" s="1"/>
+      <c r="A206" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B206">
+        <v>302</v>
+      </c>
+      <c r="C206">
+        <v>4000</v>
+      </c>
+      <c r="D206">
+        <v>6720</v>
+      </c>
+      <c r="E206">
+        <v>57</v>
+      </c>
+      <c r="F206" t="s">
+        <v>19</v>
+      </c>
+      <c r="G206">
+        <v>13</v>
+      </c>
+      <c r="H206">
+        <v>5</v>
+      </c>
+      <c r="I206">
+        <v>925</v>
+      </c>
+      <c r="K206">
+        <v>10</v>
+      </c>
+      <c r="L206">
+        <v>672</v>
+      </c>
+      <c r="M206" t="s">
+        <v>45</v>
+      </c>
       <c r="R206" s="1"/>
     </row>
     <row r="207" spans="1:18">
-      <c r="A207" s="1"/>
+      <c r="A207" s="1">
+        <v>46206</v>
+      </c>
+      <c r="B207">
+        <v>303</v>
+      </c>
+      <c r="C207">
+        <v>3600</v>
+      </c>
+      <c r="D207">
+        <v>6720</v>
+      </c>
+      <c r="E207">
+        <v>57</v>
+      </c>
+      <c r="F207" t="s">
+        <v>19</v>
+      </c>
+      <c r="G207">
+        <v>54</v>
+      </c>
+      <c r="I207">
+        <v>925</v>
+      </c>
+      <c r="K207">
+        <v>10</v>
+      </c>
+      <c r="L207">
+        <v>672</v>
+      </c>
+      <c r="M207" t="s">
+        <v>45</v>
+      </c>
       <c r="R207" s="1"/>
     </row>
     <row r="208" spans="1:18">
-      <c r="A208" s="1"/>
+      <c r="A208" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B208">
+        <v>304</v>
+      </c>
+      <c r="C208">
+        <v>6800</v>
+      </c>
+      <c r="D208">
+        <v>6720</v>
+      </c>
+      <c r="E208">
+        <v>57</v>
+      </c>
+      <c r="F208" t="s">
+        <v>19</v>
+      </c>
+      <c r="G208">
+        <v>22</v>
+      </c>
+      <c r="H208">
+        <v>8</v>
+      </c>
+      <c r="I208">
+        <v>925</v>
+      </c>
+      <c r="K208">
+        <v>10</v>
+      </c>
+      <c r="L208">
+        <v>672</v>
+      </c>
+      <c r="M208" t="s">
+        <v>45</v>
+      </c>
       <c r="R208" s="1"/>
     </row>
     <row r="209" spans="1:18">
-      <c r="A209" s="1"/>
+      <c r="A209" s="1">
+        <v>46207</v>
+      </c>
+      <c r="B209">
+        <v>305</v>
+      </c>
+      <c r="C209">
+        <v>6800</v>
+      </c>
+      <c r="D209">
+        <v>6720</v>
+      </c>
+      <c r="E209">
+        <v>57</v>
+      </c>
+      <c r="F209" t="s">
+        <v>19</v>
+      </c>
+      <c r="G209">
+        <v>42</v>
+      </c>
+      <c r="I209">
+        <v>925</v>
+      </c>
+      <c r="K209">
+        <v>10</v>
+      </c>
+      <c r="L209">
+        <v>672</v>
+      </c>
+      <c r="M209" t="s">
+        <v>45</v>
+      </c>
       <c r="R209" s="1"/>
     </row>
     <row r="210" spans="1:18">
-      <c r="A210" s="1"/>
+      <c r="A210" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B210">
+        <v>306</v>
+      </c>
+      <c r="C210">
+        <v>6800</v>
+      </c>
+      <c r="D210">
+        <v>6720</v>
+      </c>
+      <c r="E210">
+        <v>57</v>
+      </c>
+      <c r="F210" t="s">
+        <v>19</v>
+      </c>
+      <c r="G210">
+        <v>14</v>
+      </c>
+      <c r="H210">
+        <v>20</v>
+      </c>
+      <c r="I210">
+        <v>925</v>
+      </c>
+      <c r="K210">
+        <v>10</v>
+      </c>
+      <c r="L210">
+        <v>672</v>
+      </c>
+      <c r="M210" t="s">
+        <v>45</v>
+      </c>
       <c r="R210" s="1"/>
     </row>
     <row r="211" spans="1:18">

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="59">
   <si>
     <t>ENDS</t>
   </si>
@@ -7927,7 +7927,12 @@
       <c r="Q159">
         <v>9</v>
       </c>
-      <c r="R159" s="1"/>
+      <c r="R159" s="1">
+        <v>46208</v>
+      </c>
+      <c r="S159" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="160" spans="1:24">
       <c r="A160" s="1">
@@ -10094,6 +10099,15 @@
       </c>
       <c r="M208" t="s">
         <v>45</v>
+      </c>
+      <c r="O208" s="1">
+        <v>46209</v>
+      </c>
+      <c r="P208" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q208">
+        <v>9</v>
       </c>
       <c r="R208" s="1"/>
     </row>

--- a/BEAM BOOK.xlsx
+++ b/BEAM BOOK.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="59">
   <si>
     <t>ENDS</t>
   </si>
@@ -8758,7 +8758,12 @@
       <c r="Q177">
         <v>27</v>
       </c>
-      <c r="R177" s="1"/>
+      <c r="R177" s="1">
+        <v>46214</v>
+      </c>
+      <c r="S177" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="178" spans="1:25">
       <c r="A178" s="1">
@@ -9623,6 +9628,15 @@
       <c r="M196" t="s">
         <v>45</v>
       </c>
+      <c r="O196" s="1">
+        <v>46214</v>
+      </c>
+      <c r="P196" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q196">
+        <v>33</v>
+      </c>
       <c r="R196" s="1"/>
     </row>
     <row r="197" spans="1:18">
@@ -9875,6 +9889,15 @@
       <c r="M202" t="s">
         <v>45</v>
       </c>
+      <c r="O202" s="1">
+        <v>46215</v>
+      </c>
+      <c r="P202" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q202">
+        <v>34</v>
+      </c>
       <c r="R202" s="1"/>
     </row>
     <row r="203" spans="1:18">
@@ -9911,6 +9934,15 @@
       <c r="M203" t="s">
         <v>45</v>
       </c>
+      <c r="O203" s="1">
+        <v>46214</v>
+      </c>
+      <c r="P203" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q203">
+        <v>31</v>
+      </c>
       <c r="R203" s="1"/>
     </row>
     <row r="204" spans="1:18">
@@ -9950,6 +9982,15 @@
       <c r="M204" t="s">
         <v>45</v>
       </c>
+      <c r="O204" s="1">
+        <v>46214</v>
+      </c>
+      <c r="P204" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q204">
+        <v>29</v>
+      </c>
       <c r="R204" s="1"/>
     </row>
     <row r="205" spans="1:18">
@@ -9986,6 +10027,15 @@
       <c r="M205" t="s">
         <v>45</v>
       </c>
+      <c r="O205" s="1">
+        <v>46215</v>
+      </c>
+      <c r="P205" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q205">
+        <v>39</v>
+      </c>
       <c r="R205" s="1"/>
     </row>
     <row r="206" spans="1:18">
@@ -10145,6 +10195,15 @@
       <c r="M209" t="s">
         <v>45</v>
       </c>
+      <c r="O209" s="1">
+        <v>46214</v>
+      </c>
+      <c r="P209" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q209">
+        <v>30</v>
+      </c>
       <c r="R209" s="1"/>
     </row>
     <row r="210" spans="1:18">
@@ -10184,42 +10243,381 @@
       <c r="M210" t="s">
         <v>45</v>
       </c>
+      <c r="O210" s="1">
+        <v>46214</v>
+      </c>
+      <c r="P210" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q210">
+        <v>32</v>
+      </c>
       <c r="R210" s="1"/>
     </row>
     <row r="211" spans="1:18">
-      <c r="A211" s="1"/>
+      <c r="A211" s="1">
+        <v>46208</v>
+      </c>
+      <c r="B211">
+        <v>307</v>
+      </c>
+      <c r="C211">
+        <v>6800</v>
+      </c>
+      <c r="D211">
+        <v>6720</v>
+      </c>
+      <c r="E211">
+        <v>57</v>
+      </c>
+      <c r="F211" t="s">
+        <v>19</v>
+      </c>
+      <c r="G211">
+        <v>9</v>
+      </c>
+      <c r="H211">
+        <v>12</v>
+      </c>
+      <c r="I211">
+        <v>925</v>
+      </c>
+      <c r="K211">
+        <v>10</v>
+      </c>
+      <c r="L211">
+        <v>672</v>
+      </c>
+      <c r="M211" t="s">
+        <v>12</v>
+      </c>
       <c r="R211" s="1"/>
     </row>
     <row r="212" spans="1:18">
-      <c r="A212" s="1"/>
+      <c r="A212" s="1">
+        <v>46209</v>
+      </c>
+      <c r="B212">
+        <v>308</v>
+      </c>
+      <c r="C212">
+        <v>6800</v>
+      </c>
+      <c r="D212">
+        <v>6720</v>
+      </c>
+      <c r="E212">
+        <v>57</v>
+      </c>
+      <c r="F212" t="s">
+        <v>19</v>
+      </c>
+      <c r="G212">
+        <v>28</v>
+      </c>
+      <c r="H212">
+        <v>15</v>
+      </c>
+      <c r="I212">
+        <v>925</v>
+      </c>
+      <c r="K212">
+        <v>10</v>
+      </c>
+      <c r="L212">
+        <v>672</v>
+      </c>
+      <c r="M212" t="s">
+        <v>11</v>
+      </c>
+      <c r="O212" s="1">
+        <v>46215</v>
+      </c>
+      <c r="P212" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q212">
+        <v>27</v>
+      </c>
       <c r="R212" s="1"/>
     </row>
     <row r="213" spans="1:18">
-      <c r="A213" s="1"/>
+      <c r="A213" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B213">
+        <v>309</v>
+      </c>
+      <c r="C213">
+        <v>6800</v>
+      </c>
+      <c r="D213">
+        <v>6720</v>
+      </c>
+      <c r="E213">
+        <v>57</v>
+      </c>
+      <c r="F213" t="s">
+        <v>19</v>
+      </c>
+      <c r="G213">
+        <v>14</v>
+      </c>
+      <c r="H213">
+        <v>10</v>
+      </c>
+      <c r="I213">
+        <v>925</v>
+      </c>
+      <c r="K213">
+        <v>10</v>
+      </c>
+      <c r="L213">
+        <v>672</v>
+      </c>
+      <c r="M213" t="s">
+        <v>11</v>
+      </c>
+      <c r="N213" t="s">
+        <v>43</v>
+      </c>
       <c r="R213" s="1"/>
     </row>
     <row r="214" spans="1:18">
-      <c r="A214" s="1"/>
+      <c r="A214" s="1">
+        <v>46211</v>
+      </c>
+      <c r="B214">
+        <v>310</v>
+      </c>
+      <c r="C214">
+        <v>6800</v>
+      </c>
+      <c r="D214">
+        <v>6720</v>
+      </c>
+      <c r="E214">
+        <v>57</v>
+      </c>
+      <c r="F214" t="s">
+        <v>19</v>
+      </c>
+      <c r="G214">
+        <v>32</v>
+      </c>
+      <c r="H214">
+        <v>13</v>
+      </c>
+      <c r="I214">
+        <v>925</v>
+      </c>
+      <c r="K214">
+        <v>10</v>
+      </c>
+      <c r="L214">
+        <v>672</v>
+      </c>
+      <c r="M214" t="s">
+        <v>11</v>
+      </c>
+      <c r="N214" t="s">
+        <v>43</v>
+      </c>
       <c r="R214" s="1"/>
     </row>
     <row r="215" spans="1:18">
-      <c r="A215" s="1"/>
+      <c r="A215" s="1">
+        <v>46212</v>
+      </c>
+      <c r="B215">
+        <v>311</v>
+      </c>
+      <c r="C215">
+        <v>6800</v>
+      </c>
+      <c r="D215">
+        <v>6720</v>
+      </c>
+      <c r="E215">
+        <v>57</v>
+      </c>
+      <c r="F215" t="s">
+        <v>19</v>
+      </c>
+      <c r="G215">
+        <v>51</v>
+      </c>
+      <c r="H215">
+        <v>17</v>
+      </c>
+      <c r="I215">
+        <v>925</v>
+      </c>
+      <c r="K215">
+        <v>20</v>
+      </c>
+      <c r="L215">
+        <v>336</v>
+      </c>
+      <c r="M215" t="s">
+        <v>44</v>
+      </c>
       <c r="R215" s="1"/>
     </row>
     <row r="216" spans="1:18">
-      <c r="A216" s="1"/>
+      <c r="A216" s="1">
+        <v>46213</v>
+      </c>
+      <c r="B216">
+        <v>312</v>
+      </c>
+      <c r="C216">
+        <v>6800</v>
+      </c>
+      <c r="D216">
+        <v>6720</v>
+      </c>
+      <c r="E216">
+        <v>57</v>
+      </c>
+      <c r="F216" t="s">
+        <v>19</v>
+      </c>
+      <c r="G216">
+        <v>19</v>
+      </c>
+      <c r="H216">
+        <v>22</v>
+      </c>
+      <c r="I216">
+        <v>925</v>
+      </c>
+      <c r="K216">
+        <v>20</v>
+      </c>
+      <c r="L216">
+        <v>336</v>
+      </c>
+      <c r="M216" t="s">
+        <v>44</v>
+      </c>
       <c r="R216" s="1"/>
     </row>
     <row r="217" spans="1:18">
-      <c r="A217" s="1"/>
+      <c r="A217" s="1">
+        <v>46214</v>
+      </c>
+      <c r="B217">
+        <v>313</v>
+      </c>
+      <c r="C217">
+        <v>4800</v>
+      </c>
+      <c r="D217">
+        <v>4800</v>
+      </c>
+      <c r="E217">
+        <v>54</v>
+      </c>
+      <c r="F217" t="s">
+        <v>3</v>
+      </c>
+      <c r="G217">
+        <v>6</v>
+      </c>
+      <c r="H217">
+        <v>10</v>
+      </c>
+      <c r="I217">
+        <v>370</v>
+      </c>
+      <c r="K217">
+        <v>15</v>
+      </c>
+      <c r="L217">
+        <v>662</v>
+      </c>
+      <c r="M217" t="s">
+        <v>11</v>
+      </c>
       <c r="R217" s="1"/>
     </row>
     <row r="218" spans="1:18">
-      <c r="A218" s="1"/>
+      <c r="A218" s="1">
+        <v>46215</v>
+      </c>
+      <c r="B218">
+        <v>314</v>
+      </c>
+      <c r="C218">
+        <v>4800</v>
+      </c>
+      <c r="D218">
+        <v>4800</v>
+      </c>
+      <c r="E218">
+        <v>54</v>
+      </c>
+      <c r="F218" t="s">
+        <v>3</v>
+      </c>
+      <c r="G218">
+        <v>40</v>
+      </c>
+      <c r="H218">
+        <v>11</v>
+      </c>
+      <c r="I218">
+        <v>370</v>
+      </c>
+      <c r="K218">
+        <v>15</v>
+      </c>
+      <c r="L218">
+        <v>662</v>
+      </c>
+      <c r="M218" t="s">
+        <v>11</v>
+      </c>
       <c r="R218" s="1"/>
     </row>
     <row r="219" spans="1:18">
-      <c r="A219" s="1"/>
+      <c r="A219" s="1">
+        <v>46216</v>
+      </c>
+      <c r="B219">
+        <v>315</v>
+      </c>
+      <c r="C219">
+        <v>4800</v>
+      </c>
+      <c r="D219">
+        <v>4800</v>
+      </c>
+      <c r="E219">
+        <v>54</v>
+      </c>
+      <c r="F219" t="s">
+        <v>3</v>
+      </c>
+      <c r="G219">
+        <v>17</v>
+      </c>
+      <c r="H219">
+        <v>5</v>
+      </c>
+      <c r="I219">
+        <v>370</v>
+      </c>
+      <c r="K219">
+        <v>15</v>
+      </c>
+      <c r="L219">
+        <v>662</v>
+      </c>
+      <c r="M219" t="s">
+        <v>11</v>
+      </c>
       <c r="R219" s="1"/>
     </row>
     <row r="220" spans="1:18">
